--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_farming_agriculture.xlsx
@@ -1261,43 +1261,43 @@
         <v>15.4619565217391</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>274.426301519668</v>
       </c>
       <c r="G2">
         <v>1.62042197840137</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0712180414840828</v>
       </c>
       <c r="I2">
         <v>0.227529702394797</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>1592.1</v>
       </c>
       <c r="L2">
-        <v>2135.37196504185</v>
+        <v>2113.91200927194</v>
       </c>
       <c r="M2">
         <v>2010.25012054936</v>
       </c>
       <c r="N2">
-        <v>2084.57196504185</v>
+        <v>2083.72251047743</v>
       </c>
       <c r="O2">
         <v>468.950120549357</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>20.6105012054936</v>
       </c>
       <c r="Q2">
         <v>0.0800840903868603</v>
       </c>
       <c r="R2">
-        <v>0.0760029773356644</v>
+        <v>0.0760479773356644</v>
       </c>
       <c r="S2">
         <v>0.06373661666253411</v>
@@ -1319,13 +1319,13 @@
         <v>0.08489920864180669</v>
       </c>
       <c r="X2">
-        <v>0.0760029773356644</v>
+        <v>0.0763080579148125</v>
       </c>
       <c r="Y2">
         <v>0.762116351747588</v>
       </c>
       <c r="Z2">
-        <v>0.58871224504425</v>
+        <v>0.594658833378031</v>
       </c>
       <c r="AA2">
         <v>276.3</v>
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07600297733566436</v>
+        <v>0.07604797733566436</v>
       </c>
       <c r="C2">
-        <v>2135.371965041848</v>
+        <v>2113.912009271937</v>
       </c>
       <c r="D2">
-        <v>2084.571965041848</v>
+        <v>2083.72251047743</v>
       </c>
       <c r="E2">
-        <v>-468.9501205493565</v>
+        <v>-448.339619343863</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.61050120549357</v>
       </c>
       <c r="G2">
         <v>50.8</v>
@@ -1579,28 +1579,28 @@
         <v>284.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.036708210636326</v>
       </c>
       <c r="N2">
-        <v>284.5</v>
+        <v>283.4632917893637</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>284.5</v>
+        <v>283.4632917893637</v>
       </c>
       <c r="Q2">
-        <v>289.4</v>
+        <v>288.3632917893636</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07600297733566436</v>
+        <v>0.07630805791481249</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5946588333780307</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>274.426301519668</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07604797733566436</v>
+        <v>0.07609297733566436</v>
       </c>
       <c r="C3">
-        <v>2113.912009271937</v>
+        <v>2092.452745518565</v>
       </c>
       <c r="D3">
-        <v>2083.72251047743</v>
+        <v>2082.873747929552</v>
       </c>
       <c r="E3">
-        <v>-448.339619343863</v>
+        <v>-427.7291181383694</v>
       </c>
       <c r="F3">
-        <v>20.61050120549357</v>
+        <v>41.22100241098713</v>
       </c>
       <c r="G3">
         <v>50.8</v>
@@ -1661,28 +1661,28 @@
         <v>284.5</v>
       </c>
       <c r="M3">
-        <v>1.036708210636326</v>
+        <v>2.073416421272653</v>
       </c>
       <c r="N3">
-        <v>283.4632917893637</v>
+        <v>282.4265835787273</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>283.4632917893637</v>
+        <v>282.4265835787273</v>
       </c>
       <c r="Q3">
-        <v>288.3632917893636</v>
+        <v>287.3265835787273</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07630805791481249</v>
+        <v>0.07661936462822894</v>
       </c>
       <c r="T3">
-        <v>0.5946588333780307</v>
+        <v>0.6007267806573984</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>274.426301519668</v>
+        <v>137.213150759834</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07609297733566436</v>
+        <v>0.07613797733566435</v>
       </c>
       <c r="C4">
-        <v>2092.452745518565</v>
+        <v>2070.99417293644</v>
       </c>
       <c r="D4">
-        <v>2082.873747929552</v>
+        <v>2082.025676552921</v>
       </c>
       <c r="E4">
-        <v>-427.7291181383694</v>
+        <v>-407.1186169328759</v>
       </c>
       <c r="F4">
-        <v>41.22100241098713</v>
+        <v>61.8315036164807</v>
       </c>
       <c r="G4">
         <v>50.8</v>
@@ -1743,28 +1743,28 @@
         <v>284.5</v>
       </c>
       <c r="M4">
-        <v>2.073416421272653</v>
+        <v>3.110124631908979</v>
       </c>
       <c r="N4">
-        <v>282.4265835787273</v>
+        <v>281.389875368091</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>282.4265835787273</v>
+        <v>281.389875368091</v>
       </c>
       <c r="Q4">
-        <v>287.3265835787273</v>
+        <v>286.289875368091</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07661936462822894</v>
+        <v>0.07693709003676738</v>
       </c>
       <c r="T4">
-        <v>0.6007267806573984</v>
+        <v>0.6069198402518045</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>137.213150759834</v>
+        <v>91.47543383988933</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07613797733566435</v>
+        <v>0.07618297733566437</v>
       </c>
       <c r="C5">
-        <v>2070.99417293644</v>
+        <v>2049.536290681645</v>
       </c>
       <c r="D5">
-        <v>2082.025676552921</v>
+        <v>2081.178295503619</v>
       </c>
       <c r="E5">
-        <v>-407.1186169328759</v>
+        <v>-386.5081157273823</v>
       </c>
       <c r="F5">
-        <v>61.8315036164807</v>
+        <v>82.44200482197427</v>
       </c>
       <c r="G5">
         <v>50.8</v>
@@ -1825,28 +1825,28 @@
         <v>284.5</v>
       </c>
       <c r="M5">
-        <v>3.110124631908979</v>
+        <v>4.146832842545305</v>
       </c>
       <c r="N5">
-        <v>281.389875368091</v>
+        <v>280.3531671574547</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>281.389875368091</v>
+        <v>280.3531671574547</v>
       </c>
       <c r="Q5">
-        <v>286.289875368091</v>
+        <v>285.2531671574547</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07693709003676738</v>
+        <v>0.07726143472465039</v>
       </c>
       <c r="T5">
-        <v>0.6069198402518045</v>
+        <v>0.6132419219210942</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>91.47543383988933</v>
+        <v>68.60657537991702</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07618297733566437</v>
+        <v>0.07622797733566436</v>
       </c>
       <c r="C6">
-        <v>2049.536290681645</v>
+        <v>2028.079097911637</v>
       </c>
       <c r="D6">
-        <v>2081.178295503619</v>
+        <v>2080.331603939104</v>
       </c>
       <c r="E6">
-        <v>-386.5081157273823</v>
+        <v>-365.8976145218887</v>
       </c>
       <c r="F6">
-        <v>82.44200482197427</v>
+        <v>103.0525060274678</v>
       </c>
       <c r="G6">
         <v>50.8</v>
@@ -1907,28 +1907,28 @@
         <v>284.5</v>
       </c>
       <c r="M6">
-        <v>4.146832842545305</v>
+        <v>5.183541053181631</v>
       </c>
       <c r="N6">
-        <v>280.3531671574547</v>
+        <v>279.3164589468184</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>280.3531671574547</v>
+        <v>279.3164589468184</v>
       </c>
       <c r="Q6">
-        <v>285.2531671574547</v>
+        <v>284.2164589468184</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07726143472465039</v>
+        <v>0.07759260772175196</v>
       </c>
       <c r="T6">
-        <v>0.6132419219210942</v>
+        <v>0.6196971000465793</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.60657537991702</v>
+        <v>54.88526030393361</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07622797733566436</v>
+        <v>0.07627297733566436</v>
       </c>
       <c r="C7">
-        <v>2028.079097911637</v>
+        <v>2006.622593785242</v>
       </c>
       <c r="D7">
-        <v>2080.331603939104</v>
+        <v>2079.485601018203</v>
       </c>
       <c r="E7">
-        <v>-365.8976145218887</v>
+        <v>-345.2871133163951</v>
       </c>
       <c r="F7">
-        <v>103.0525060274678</v>
+        <v>123.6630072329614</v>
       </c>
       <c r="G7">
         <v>50.8</v>
@@ -1989,28 +1989,28 @@
         <v>284.5</v>
       </c>
       <c r="M7">
-        <v>5.183541053181631</v>
+        <v>6.220249263817959</v>
       </c>
       <c r="N7">
-        <v>279.3164589468184</v>
+        <v>278.2797507361821</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>279.3164589468184</v>
+        <v>278.2797507361821</v>
       </c>
       <c r="Q7">
-        <v>284.2164589468184</v>
+        <v>283.179750736182</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07759260772175196</v>
+        <v>0.07793082695283443</v>
       </c>
       <c r="T7">
-        <v>0.6196971000465793</v>
+        <v>0.6262896223875004</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.88526030393361</v>
+        <v>45.73771691994467</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07627297733566435</v>
+        <v>0.07631797733566435</v>
       </c>
       <c r="C8">
-        <v>2006.622593785242</v>
+        <v>1985.166777462655</v>
       </c>
       <c r="D8">
-        <v>2079.485601018203</v>
+        <v>2078.64028590111</v>
       </c>
       <c r="E8">
-        <v>-345.2871133163952</v>
+        <v>-324.6766121109016</v>
       </c>
       <c r="F8">
-        <v>123.6630072329614</v>
+        <v>144.2735084384549</v>
       </c>
       <c r="G8">
         <v>50.8</v>
@@ -2071,28 +2071,28 @@
         <v>284.5</v>
       </c>
       <c r="M8">
-        <v>6.220249263817958</v>
+        <v>7.256957474454283</v>
       </c>
       <c r="N8">
-        <v>278.2797507361821</v>
+        <v>277.2430425255457</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>278.2797507361821</v>
+        <v>277.2430425255457</v>
       </c>
       <c r="Q8">
-        <v>283.179750736182</v>
+        <v>282.1430425255457</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07793082695283443</v>
+        <v>0.07827631971576812</v>
       </c>
       <c r="T8">
-        <v>0.6262896223875004</v>
+        <v>0.6330239194024196</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.73771691994467</v>
+        <v>39.20375735995258</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07631797733566434</v>
+        <v>0.07636297733566436</v>
       </c>
       <c r="C9">
-        <v>1985.166777462656</v>
+        <v>1963.711648105437</v>
       </c>
       <c r="D9">
-        <v>2078.64028590111</v>
+        <v>2077.795657749386</v>
       </c>
       <c r="E9">
-        <v>-324.6766121109016</v>
+        <v>-304.066110905408</v>
       </c>
       <c r="F9">
-        <v>144.273508438455</v>
+        <v>164.8840096439485</v>
       </c>
       <c r="G9">
         <v>50.8</v>
@@ -2153,28 +2153,28 @@
         <v>284.5</v>
       </c>
       <c r="M9">
-        <v>7.256957474454285</v>
+        <v>8.293665685090611</v>
       </c>
       <c r="N9">
-        <v>277.2430425255457</v>
+        <v>276.2063343149094</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>277.2430425255457</v>
+        <v>276.2063343149094</v>
       </c>
       <c r="Q9">
-        <v>282.1430425255457</v>
+        <v>281.1063343149094</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07827631971576812</v>
+        <v>0.07862932319093952</v>
       </c>
       <c r="T9">
-        <v>0.6330239194024196</v>
+        <v>0.6399046141785329</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.20375735995258</v>
+        <v>34.3032876899585</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07636297733566436</v>
+        <v>0.07640797733566437</v>
       </c>
       <c r="C10">
-        <v>1963.711648105437</v>
+        <v>1942.25720487651</v>
       </c>
       <c r="D10">
-        <v>2077.795657749386</v>
+        <v>2076.951715725952</v>
       </c>
       <c r="E10">
-        <v>-304.066110905408</v>
+        <v>-283.4556096999145</v>
       </c>
       <c r="F10">
-        <v>164.8840096439485</v>
+        <v>185.4945108494421</v>
       </c>
       <c r="G10">
         <v>50.8</v>
@@ -2235,28 +2235,28 @@
         <v>284.5</v>
       </c>
       <c r="M10">
-        <v>8.293665685090611</v>
+        <v>9.330373895726936</v>
       </c>
       <c r="N10">
-        <v>276.2063343149094</v>
+        <v>275.169626104273</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>276.2063343149094</v>
+        <v>275.169626104273</v>
       </c>
       <c r="Q10">
-        <v>281.1063343149094</v>
+        <v>280.069626104273</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07862932319093952</v>
+        <v>0.07899008498424656</v>
       </c>
       <c r="T10">
-        <v>0.6399046141785329</v>
+        <v>0.6469365330156598</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.3032876899585</v>
+        <v>30.49181127996312</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07640797733566437</v>
+        <v>0.07645297733566436</v>
       </c>
       <c r="C11">
-        <v>1942.25720487651</v>
+        <v>1920.803446940155</v>
       </c>
       <c r="D11">
-        <v>2076.951715725952</v>
+        <v>2076.108458995091</v>
       </c>
       <c r="E11">
-        <v>-283.4556096999145</v>
+        <v>-262.8451084944209</v>
       </c>
       <c r="F11">
-        <v>185.4945108494421</v>
+        <v>206.1050120549356</v>
       </c>
       <c r="G11">
         <v>50.8</v>
@@ -2317,28 +2317,28 @@
         <v>284.5</v>
       </c>
       <c r="M11">
-        <v>9.330373895726936</v>
+        <v>10.36708210636326</v>
       </c>
       <c r="N11">
-        <v>275.169626104273</v>
+        <v>274.1329178936367</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>275.169626104273</v>
+        <v>274.1329178936367</v>
       </c>
       <c r="Q11">
-        <v>280.069626104273</v>
+        <v>279.0329178936367</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07899008498424656</v>
+        <v>0.07935886370629373</v>
       </c>
       <c r="T11">
-        <v>0.6469365330156598</v>
+        <v>0.6541247167158337</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.49181127996312</v>
+        <v>27.44263015196681</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07645297733566436</v>
+        <v>0.07649797733566435</v>
       </c>
       <c r="C12">
-        <v>1920.803446940155</v>
+        <v>1899.35037346201</v>
       </c>
       <c r="D12">
-        <v>2076.108458995091</v>
+        <v>2075.265886722439</v>
       </c>
       <c r="E12">
-        <v>-262.8451084944209</v>
+        <v>-242.2346072889273</v>
       </c>
       <c r="F12">
-        <v>206.1050120549357</v>
+        <v>226.7155132604292</v>
       </c>
       <c r="G12">
         <v>50.8</v>
@@ -2399,28 +2399,28 @@
         <v>284.5</v>
       </c>
       <c r="M12">
-        <v>10.36708210636326</v>
+        <v>11.40379031699959</v>
       </c>
       <c r="N12">
-        <v>274.1329178936367</v>
+        <v>273.0962096830004</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>274.1329178936367</v>
+        <v>273.0962096830004</v>
       </c>
       <c r="Q12">
-        <v>279.0329178936367</v>
+        <v>277.9962096830004</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07935886370629373</v>
+        <v>0.07973592959063411</v>
       </c>
       <c r="T12">
-        <v>0.6541247167158337</v>
+        <v>0.6614744326339892</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.4426301519668</v>
+        <v>24.9478455926971</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07649797733566435</v>
+        <v>0.07654297733566437</v>
       </c>
       <c r="C13">
-        <v>1899.35037346201</v>
+        <v>1877.897983609067</v>
       </c>
       <c r="D13">
-        <v>2075.265886722439</v>
+        <v>2074.42399807499</v>
       </c>
       <c r="E13">
-        <v>-242.2346072889273</v>
+        <v>-221.6241060834338</v>
       </c>
       <c r="F13">
-        <v>226.7155132604292</v>
+        <v>247.3260144659228</v>
       </c>
       <c r="G13">
         <v>50.8</v>
@@ -2481,28 +2481,28 @@
         <v>284.5</v>
       </c>
       <c r="M13">
-        <v>11.40379031699959</v>
+        <v>12.44049852763592</v>
       </c>
       <c r="N13">
-        <v>273.0962096830004</v>
+        <v>272.0595014723641</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>273.0962096830004</v>
+        <v>272.0595014723641</v>
       </c>
       <c r="Q13">
-        <v>277.9962096830004</v>
+        <v>276.9595014723641</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07973592959063411</v>
+        <v>0.08012156515416405</v>
       </c>
       <c r="T13">
-        <v>0.6614744326339892</v>
+        <v>0.6689911875502844</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.9478455926971</v>
+        <v>22.86885845997234</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07654297733566437</v>
+        <v>0.07658797733566436</v>
       </c>
       <c r="C14">
-        <v>1877.897983609067</v>
+        <v>1856.446276549671</v>
       </c>
       <c r="D14">
-        <v>2074.42399807499</v>
+        <v>2073.582792221087</v>
       </c>
       <c r="E14">
-        <v>-221.6241060834338</v>
+        <v>-201.0136048779402</v>
       </c>
       <c r="F14">
-        <v>247.3260144659228</v>
+        <v>267.9365156714164</v>
       </c>
       <c r="G14">
         <v>50.8</v>
@@ -2563,28 +2563,28 @@
         <v>284.5</v>
       </c>
       <c r="M14">
-        <v>12.44049852763592</v>
+        <v>13.47720673827224</v>
       </c>
       <c r="N14">
-        <v>272.0595014723641</v>
+        <v>271.0227932617278</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>272.0595014723641</v>
+        <v>271.0227932617278</v>
       </c>
       <c r="Q14">
-        <v>276.9595014723641</v>
+        <v>275.9227932617277</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08012156515416405</v>
+        <v>0.08051606590306248</v>
       </c>
       <c r="T14">
-        <v>0.6689911875502844</v>
+        <v>0.6766807414301728</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.86885845997234</v>
+        <v>21.10971550151293</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07658797733566436</v>
+        <v>0.07663297733566436</v>
       </c>
       <c r="C15">
-        <v>1856.446276549671</v>
+        <v>1834.995251453512</v>
       </c>
       <c r="D15">
-        <v>2073.582792221087</v>
+        <v>2072.742268330422</v>
       </c>
       <c r="E15">
-        <v>-201.0136048779402</v>
+        <v>-180.4031036724466</v>
       </c>
       <c r="F15">
-        <v>267.9365156714164</v>
+        <v>288.5470168769099</v>
       </c>
       <c r="G15">
         <v>50.8</v>
@@ -2645,28 +2645,28 @@
         <v>284.5</v>
       </c>
       <c r="M15">
-        <v>13.47720673827224</v>
+        <v>14.51391494890857</v>
       </c>
       <c r="N15">
-        <v>271.0227932617278</v>
+        <v>269.9860850510914</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>271.0227932617278</v>
+        <v>269.9860850510914</v>
       </c>
       <c r="Q15">
-        <v>275.9227932617277</v>
+        <v>274.8860850510914</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08051606590306248</v>
+        <v>0.08091974108798181</v>
       </c>
       <c r="T15">
-        <v>0.6766807414301728</v>
+        <v>0.6845491221444772</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.10971550151293</v>
+        <v>19.60187867997629</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07663297733566436</v>
+        <v>0.07667797733566437</v>
       </c>
       <c r="C16">
-        <v>1834.995251453512</v>
+        <v>1813.544907491628</v>
       </c>
       <c r="D16">
-        <v>2072.742268330422</v>
+        <v>2071.902425574031</v>
       </c>
       <c r="E16">
-        <v>-180.4031036724466</v>
+        <v>-159.792602466953</v>
       </c>
       <c r="F16">
-        <v>288.5470168769099</v>
+        <v>309.1575180824035</v>
       </c>
       <c r="G16">
         <v>50.8</v>
@@ -2727,28 +2727,28 @@
         <v>284.5</v>
       </c>
       <c r="M16">
-        <v>14.51391494890857</v>
+        <v>15.55062315954489</v>
       </c>
       <c r="N16">
-        <v>269.9860850510914</v>
+        <v>268.9493768404551</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>269.9860850510914</v>
+        <v>268.9493768404551</v>
       </c>
       <c r="Q16">
-        <v>274.8860850510914</v>
+        <v>273.8493768404551</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08091974108798181</v>
+        <v>0.08133291451254632</v>
       </c>
       <c r="T16">
-        <v>0.6845491221444772</v>
+        <v>0.6926026412285299</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.60187867997629</v>
+        <v>18.29508676797787</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07667797733566437</v>
+        <v>0.07672297733566436</v>
       </c>
       <c r="C17">
-        <v>1813.544907491628</v>
+        <v>1792.0952438364</v>
       </c>
       <c r="D17">
-        <v>2071.902425574031</v>
+        <v>2071.063263124297</v>
       </c>
       <c r="E17">
-        <v>-159.7926024669531</v>
+        <v>-139.1821012614595</v>
       </c>
       <c r="F17">
-        <v>309.1575180824034</v>
+        <v>329.7680192878971</v>
       </c>
       <c r="G17">
         <v>50.8</v>
@@ -2809,28 +2809,28 @@
         <v>284.5</v>
       </c>
       <c r="M17">
-        <v>15.55062315954489</v>
+        <v>16.58733137018122</v>
       </c>
       <c r="N17">
-        <v>268.9493768404551</v>
+        <v>267.9126686298188</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>268.9493768404551</v>
+        <v>267.9126686298188</v>
       </c>
       <c r="Q17">
-        <v>273.8493768404551</v>
+        <v>272.8126686298187</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08133291451254632</v>
+        <v>0.08175592539960043</v>
       </c>
       <c r="T17">
-        <v>0.6926026412285299</v>
+        <v>0.7008479107669647</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.29508676797787</v>
+        <v>17.15164384497925</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07672297733566436</v>
+        <v>0.07676797733566436</v>
       </c>
       <c r="C18">
-        <v>1792.0952438364</v>
+        <v>1770.646259661547</v>
       </c>
       <c r="D18">
-        <v>2071.063263124297</v>
+        <v>2070.224780154938</v>
       </c>
       <c r="E18">
-        <v>-139.1821012614595</v>
+        <v>-118.5716000559659</v>
       </c>
       <c r="F18">
-        <v>329.7680192878971</v>
+        <v>350.3785204933906</v>
       </c>
       <c r="G18">
         <v>50.8</v>
@@ -2891,28 +2891,28 @@
         <v>284.5</v>
       </c>
       <c r="M18">
-        <v>16.58733137018122</v>
+        <v>17.62403958081755</v>
       </c>
       <c r="N18">
-        <v>267.9126686298188</v>
+        <v>266.8759604191824</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>267.9126686298188</v>
+        <v>266.8759604191824</v>
       </c>
       <c r="Q18">
-        <v>272.8126686298187</v>
+        <v>271.7759604191824</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08175592539960043</v>
+        <v>0.08218912932007755</v>
       </c>
       <c r="T18">
-        <v>0.7008479107669647</v>
+        <v>0.7092918614990968</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.15164384497925</v>
+        <v>16.142723618804</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07676797733566436</v>
+        <v>0.07681297733566436</v>
       </c>
       <c r="C19">
-        <v>1770.646259661547</v>
+        <v>1749.19795414213</v>
       </c>
       <c r="D19">
-        <v>2070.224780154938</v>
+        <v>2069.386975841014</v>
       </c>
       <c r="E19">
-        <v>-118.5716000559659</v>
+        <v>-97.96109885047235</v>
       </c>
       <c r="F19">
-        <v>350.3785204933906</v>
+        <v>370.9890216988842</v>
       </c>
       <c r="G19">
         <v>50.8</v>
@@ -2973,28 +2973,28 @@
         <v>284.5</v>
       </c>
       <c r="M19">
-        <v>17.62403958081755</v>
+        <v>18.66074779145387</v>
       </c>
       <c r="N19">
-        <v>266.8759604191824</v>
+        <v>265.8392522085461</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>266.8759604191824</v>
+        <v>265.8392522085461</v>
       </c>
       <c r="Q19">
-        <v>271.7759604191824</v>
+        <v>270.7392522085461</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08218912932007755</v>
+        <v>0.08263289918983459</v>
       </c>
       <c r="T19">
-        <v>0.7092918614990968</v>
+        <v>0.7179417622490858</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.142723618804</v>
+        <v>15.24590563998156</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07681297733566436</v>
+        <v>0.07685797733566437</v>
       </c>
       <c r="C20">
-        <v>1749.19795414213</v>
+        <v>1727.75032645454</v>
       </c>
       <c r="D20">
-        <v>2069.386975841014</v>
+        <v>2068.549849358918</v>
       </c>
       <c r="E20">
-        <v>-97.96109885047241</v>
+        <v>-77.35059764497879</v>
       </c>
       <c r="F20">
-        <v>370.9890216988841</v>
+        <v>391.5995229043777</v>
       </c>
       <c r="G20">
         <v>50.8</v>
@@ -3055,28 +3055,28 @@
         <v>284.5</v>
       </c>
       <c r="M20">
-        <v>18.66074779145387</v>
+        <v>19.6974560020902</v>
       </c>
       <c r="N20">
-        <v>265.8392522085461</v>
+        <v>264.8025439979098</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>265.8392522085461</v>
+        <v>264.8025439979098</v>
       </c>
       <c r="Q20">
-        <v>270.7392522085461</v>
+        <v>269.7025439979098</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08263289918983459</v>
+        <v>0.08308762634032638</v>
       </c>
       <c r="T20">
-        <v>0.7179417622490858</v>
+        <v>0.7268052407953708</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.24590563998156</v>
+        <v>14.44348955366674</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07685797733566437</v>
+        <v>0.07690297733566435</v>
       </c>
       <c r="C21">
-        <v>1727.75032645454</v>
+        <v>1706.303375776503</v>
       </c>
       <c r="D21">
-        <v>2068.549849358918</v>
+        <v>2067.713399886374</v>
       </c>
       <c r="E21">
-        <v>-77.35059764497879</v>
+        <v>-56.74009643948523</v>
       </c>
       <c r="F21">
-        <v>391.5995229043777</v>
+        <v>412.2100241098713</v>
       </c>
       <c r="G21">
         <v>50.8</v>
@@ -3137,28 +3137,28 @@
         <v>284.5</v>
       </c>
       <c r="M21">
-        <v>19.6974560020902</v>
+        <v>20.73416421272653</v>
       </c>
       <c r="N21">
-        <v>264.8025439979098</v>
+        <v>263.7658357872735</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>264.8025439979098</v>
+        <v>263.7658357872735</v>
       </c>
       <c r="Q21">
-        <v>269.7025439979098</v>
+        <v>268.6658357872735</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08308762634032638</v>
+        <v>0.08355372166958044</v>
       </c>
       <c r="T21">
-        <v>0.7268052407953708</v>
+        <v>0.7358903063053129</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.44348955366674</v>
+        <v>13.7213150759834</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07690297733566435</v>
+        <v>0.07694797733566437</v>
       </c>
       <c r="C22">
-        <v>1706.303375776503</v>
+        <v>1684.857101287074</v>
       </c>
       <c r="D22">
-        <v>2067.713399886374</v>
+        <v>2066.877626602438</v>
       </c>
       <c r="E22">
-        <v>-56.74009643948523</v>
+        <v>-36.12959523399161</v>
       </c>
       <c r="F22">
-        <v>412.2100241098713</v>
+        <v>432.8205253153649</v>
       </c>
       <c r="G22">
         <v>50.8</v>
@@ -3219,28 +3219,28 @@
         <v>284.5</v>
       </c>
       <c r="M22">
-        <v>20.73416421272653</v>
+        <v>21.77087242336286</v>
       </c>
       <c r="N22">
-        <v>263.7658357872735</v>
+        <v>262.7291275766372</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>263.7658357872735</v>
+        <v>262.7291275766372</v>
       </c>
       <c r="Q22">
-        <v>268.6658357872735</v>
+        <v>267.6291275766371</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08355372166958044</v>
+        <v>0.0840316168805878</v>
       </c>
       <c r="T22">
-        <v>0.7358903063053129</v>
+        <v>0.7452053734737347</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.7213150759834</v>
+        <v>13.06791911998419</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07694797733566437</v>
+        <v>0.07732297733566436</v>
       </c>
       <c r="C23">
-        <v>1684.857101287074</v>
+        <v>1657.308009475018</v>
       </c>
       <c r="D23">
-        <v>2066.877626602438</v>
+        <v>2059.939035995877</v>
       </c>
       <c r="E23">
-        <v>-36.12959523399167</v>
+        <v>-15.5190940284981</v>
       </c>
       <c r="F23">
-        <v>432.8205253153649</v>
+        <v>453.4310265208584</v>
       </c>
       <c r="G23">
         <v>50.8</v>
@@ -3301,45 +3301,45 @@
         <v>284.5</v>
       </c>
       <c r="M23">
-        <v>21.77087242336285</v>
+        <v>23.48772717378047</v>
       </c>
       <c r="N23">
-        <v>262.7291275766372</v>
+        <v>261.0122728262195</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>262.7291275766372</v>
+        <v>261.0122728262195</v>
       </c>
       <c r="Q23">
-        <v>267.6291275766371</v>
+        <v>265.9122728262195</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0840316168805878</v>
+        <v>0.0845217658149543</v>
       </c>
       <c r="T23">
-        <v>0.7452053734737347</v>
+        <v>0.7547592885182696</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.06791911998419</v>
+        <v>12.1127088157593</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07732297733566436</v>
+        <v>0.07738297733566438</v>
       </c>
       <c r="C24">
-        <v>1657.308009475018</v>
+        <v>1635.591654655676</v>
       </c>
       <c r="D24">
-        <v>2059.939035995877</v>
+        <v>2058.833182382028</v>
       </c>
       <c r="E24">
-        <v>-15.5190940284981</v>
+        <v>5.09140717699546</v>
       </c>
       <c r="F24">
-        <v>453.4310265208584</v>
+        <v>474.041527726352</v>
       </c>
       <c r="G24">
         <v>50.8</v>
@@ -3383,28 +3383,28 @@
         <v>284.5</v>
       </c>
       <c r="M24">
-        <v>23.48772717378047</v>
+        <v>24.55535113622503</v>
       </c>
       <c r="N24">
-        <v>261.0122728262195</v>
+        <v>259.9446488637749</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>261.0122728262195</v>
+        <v>259.9446488637749</v>
       </c>
       <c r="Q24">
-        <v>265.9122728262195</v>
+        <v>264.8446488637749</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0845217658149543</v>
+        <v>0.0850246458904732</v>
       </c>
       <c r="T24">
-        <v>0.7547592885182696</v>
+        <v>0.7645613572003251</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.1127088157593</v>
+        <v>11.58606930203064</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07738297733566438</v>
+        <v>0.07744297733566435</v>
       </c>
       <c r="C25">
-        <v>1635.591654655676</v>
+        <v>1613.876486527824</v>
       </c>
       <c r="D25">
-        <v>2058.833182382028</v>
+        <v>2057.72851545967</v>
       </c>
       <c r="E25">
-        <v>5.09140717699546</v>
+        <v>25.70190838248908</v>
       </c>
       <c r="F25">
-        <v>474.041527726352</v>
+        <v>494.6520289318456</v>
       </c>
       <c r="G25">
         <v>50.8</v>
@@ -3465,28 +3465,28 @@
         <v>284.5</v>
       </c>
       <c r="M25">
-        <v>24.55535113622503</v>
+        <v>25.6229750986696</v>
       </c>
       <c r="N25">
-        <v>259.9446488637749</v>
+        <v>258.8770249013304</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>259.9446488637749</v>
+        <v>258.8770249013304</v>
       </c>
       <c r="Q25">
-        <v>264.8446488637749</v>
+        <v>263.7770249013304</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0850246458904732</v>
+        <v>0.08554075965218995</v>
       </c>
       <c r="T25">
-        <v>0.7645613572003251</v>
+        <v>0.7746213750582241</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.58606930203064</v>
+        <v>11.10331641444603</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07744297733566435</v>
+        <v>0.07750297733566436</v>
       </c>
       <c r="C26">
-        <v>1613.876486527824</v>
+        <v>1592.162503182328</v>
       </c>
       <c r="D26">
-        <v>2057.72851545967</v>
+        <v>2056.625033319667</v>
       </c>
       <c r="E26">
-        <v>25.70190838248902</v>
+        <v>46.31240958798259</v>
       </c>
       <c r="F26">
-        <v>494.6520289318456</v>
+        <v>515.2625301373391</v>
       </c>
       <c r="G26">
         <v>50.8</v>
@@ -3547,28 +3547,28 @@
         <v>284.5</v>
       </c>
       <c r="M26">
-        <v>25.6229750986696</v>
+        <v>26.69059906111417</v>
       </c>
       <c r="N26">
-        <v>258.8770249013304</v>
+        <v>257.8094009388859</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>258.8770249013304</v>
+        <v>257.8094009388859</v>
       </c>
       <c r="Q26">
-        <v>263.7770249013304</v>
+        <v>262.7094009388858</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08554075965218995</v>
+        <v>0.08607063644755247</v>
       </c>
       <c r="T26">
-        <v>0.7746213750582241</v>
+        <v>0.7849496600590005</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.10331641444603</v>
+        <v>10.65918375786819</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07750297733566436</v>
+        <v>0.07756297733566436</v>
       </c>
       <c r="C27">
-        <v>1592.162503182328</v>
+        <v>1570.449702714147</v>
       </c>
       <c r="D27">
-        <v>2056.625033319667</v>
+        <v>2055.52273405698</v>
       </c>
       <c r="E27">
-        <v>46.31240958798259</v>
+        <v>66.92291079347621</v>
       </c>
       <c r="F27">
-        <v>515.2625301373391</v>
+        <v>535.8730313428327</v>
       </c>
       <c r="G27">
         <v>50.8</v>
@@ -3629,28 +3629,28 @@
         <v>284.5</v>
       </c>
       <c r="M27">
-        <v>26.69059906111417</v>
+        <v>27.75822302355873</v>
       </c>
       <c r="N27">
-        <v>257.8094009388859</v>
+        <v>256.7417769764413</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>257.8094009388859</v>
+        <v>256.7417769764413</v>
       </c>
       <c r="Q27">
-        <v>262.7094009388858</v>
+        <v>261.6417769764412</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08607063644755247</v>
+        <v>0.08661483423738427</v>
       </c>
       <c r="T27">
-        <v>0.7849496600590005</v>
+        <v>0.7955570878976356</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.65918375786819</v>
+        <v>10.24921515179633</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07756297733566436</v>
+        <v>0.07762297733566435</v>
       </c>
       <c r="C28">
-        <v>1570.449702714147</v>
+        <v>1548.738083222324</v>
       </c>
       <c r="D28">
-        <v>2055.52273405698</v>
+        <v>2054.421615770651</v>
       </c>
       <c r="E28">
-        <v>66.92291079347621</v>
+        <v>87.53341199896971</v>
       </c>
       <c r="F28">
-        <v>535.8730313428327</v>
+        <v>556.4835325483263</v>
       </c>
       <c r="G28">
         <v>50.8</v>
@@ -3711,28 +3711,28 @@
         <v>284.5</v>
       </c>
       <c r="M28">
-        <v>27.75822302355873</v>
+        <v>28.8258469860033</v>
       </c>
       <c r="N28">
-        <v>256.7417769764413</v>
+        <v>255.6741530139967</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>256.7417769764413</v>
+        <v>255.6741530139967</v>
       </c>
       <c r="Q28">
-        <v>261.6417769764412</v>
+        <v>260.5741530139967</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08661483423738427</v>
+        <v>0.0871739415557046</v>
       </c>
       <c r="T28">
-        <v>0.7955570878976356</v>
+        <v>0.8064551301976033</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.24921515179633</v>
+        <v>9.869614590618692</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07762297733566435</v>
+        <v>0.07815897733566436</v>
       </c>
       <c r="C29">
-        <v>1548.738083222324</v>
+        <v>1518.343018505092</v>
       </c>
       <c r="D29">
-        <v>2054.421615770651</v>
+        <v>2044.637052258912</v>
       </c>
       <c r="E29">
-        <v>87.53341199896971</v>
+        <v>108.1439132044633</v>
       </c>
       <c r="F29">
-        <v>556.4835325483263</v>
+        <v>577.0940337538199</v>
       </c>
       <c r="G29">
         <v>50.8</v>
@@ -3793,45 +3793,45 @@
         <v>284.5</v>
       </c>
       <c r="M29">
-        <v>28.8258469860033</v>
+        <v>30.87453080582936</v>
       </c>
       <c r="N29">
-        <v>255.6741530139967</v>
+        <v>253.6254691941706</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>255.6741530139967</v>
+        <v>253.6254691941706</v>
       </c>
       <c r="Q29">
-        <v>260.5741530139967</v>
+        <v>258.5254691941706</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0871739415557046</v>
+        <v>0.08774857963286717</v>
       </c>
       <c r="T29">
-        <v>0.8064551301976033</v>
+        <v>0.8176558958947922</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.869614590618692</v>
+        <v>9.214714930867357</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07815897733566436</v>
+        <v>0.07823597733566436</v>
       </c>
       <c r="C30">
-        <v>1518.343018505092</v>
+        <v>1496.334550028926</v>
       </c>
       <c r="D30">
-        <v>2044.637052258912</v>
+        <v>2043.23908498824</v>
       </c>
       <c r="E30">
-        <v>108.1439132044633</v>
+        <v>128.754414409957</v>
       </c>
       <c r="F30">
-        <v>577.0940337538199</v>
+        <v>597.7045349593135</v>
       </c>
       <c r="G30">
         <v>50.8</v>
@@ -3875,28 +3875,28 @@
         <v>284.5</v>
       </c>
       <c r="M30">
-        <v>30.87453080582936</v>
+        <v>31.97719262032327</v>
       </c>
       <c r="N30">
-        <v>253.6254691941706</v>
+        <v>252.5228073796767</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>253.6254691941706</v>
+        <v>252.5228073796767</v>
       </c>
       <c r="Q30">
-        <v>258.5254691941706</v>
+        <v>257.4228073796767</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08774857963286717</v>
+        <v>0.08833940469811882</v>
       </c>
       <c r="T30">
-        <v>0.8176558958947922</v>
+        <v>0.8291721761186626</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.214714930867357</v>
+        <v>8.896966140147793</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07823597733566436</v>
+        <v>0.07831297733566435</v>
       </c>
       <c r="C31">
-        <v>1496.334550028926</v>
+        <v>1474.327991893954</v>
       </c>
       <c r="D31">
-        <v>2043.23908498824</v>
+        <v>2041.843028058761</v>
       </c>
       <c r="E31">
-        <v>128.7544144099568</v>
+        <v>149.3649156154503</v>
       </c>
       <c r="F31">
-        <v>597.7045349593134</v>
+        <v>618.3150361648069</v>
       </c>
       <c r="G31">
         <v>50.8</v>
@@ -3957,28 +3957,28 @@
         <v>284.5</v>
       </c>
       <c r="M31">
-        <v>31.97719262032327</v>
+        <v>33.07985443481716</v>
       </c>
       <c r="N31">
-        <v>252.5228073796767</v>
+        <v>251.4201455651828</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>252.5228073796767</v>
+        <v>251.4201455651828</v>
       </c>
       <c r="Q31">
-        <v>257.4228073796767</v>
+        <v>256.3201455651828</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08833940469811882</v>
+        <v>0.08894711047952052</v>
       </c>
       <c r="T31">
-        <v>0.8291721761186625</v>
+        <v>0.8410174929203577</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.896966140147795</v>
+        <v>8.600400602142869</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07831297733566435</v>
+        <v>0.07838997733566436</v>
       </c>
       <c r="C32">
-        <v>1474.327991893954</v>
+        <v>1452.323340187087</v>
       </c>
       <c r="D32">
-        <v>2041.843028058761</v>
+        <v>2040.448877557387</v>
       </c>
       <c r="E32">
-        <v>149.3649156154503</v>
+        <v>169.975416820944</v>
       </c>
       <c r="F32">
-        <v>618.3150361648069</v>
+        <v>638.9255373703005</v>
       </c>
       <c r="G32">
         <v>50.8</v>
@@ -4039,28 +4039,28 @@
         <v>284.5</v>
       </c>
       <c r="M32">
-        <v>33.07985443481716</v>
+        <v>34.18251624931108</v>
       </c>
       <c r="N32">
-        <v>251.4201455651828</v>
+        <v>250.3174837506889</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>251.4201455651828</v>
+        <v>250.3174837506889</v>
       </c>
       <c r="Q32">
-        <v>256.3201455651828</v>
+        <v>255.2174837506889</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08894711047952052</v>
+        <v>0.08957243092125269</v>
       </c>
       <c r="T32">
-        <v>0.8410174929203577</v>
+        <v>0.853206152238044</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.600400602142869</v>
+        <v>8.322968324654386</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07838997733566436</v>
+        <v>0.07846697733566435</v>
       </c>
       <c r="C33">
-        <v>1452.323340187087</v>
+        <v>1430.320591005919</v>
       </c>
       <c r="D33">
-        <v>2040.448877557387</v>
+        <v>2039.056629581713</v>
       </c>
       <c r="E33">
-        <v>169.975416820944</v>
+        <v>190.5859180264376</v>
       </c>
       <c r="F33">
-        <v>638.9255373703005</v>
+        <v>659.5360385757941</v>
       </c>
       <c r="G33">
         <v>50.8</v>
@@ -4121,28 +4121,28 @@
         <v>284.5</v>
       </c>
       <c r="M33">
-        <v>34.18251624931108</v>
+        <v>35.28517806380498</v>
       </c>
       <c r="N33">
-        <v>250.3174837506889</v>
+        <v>249.214821936195</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>250.3174837506889</v>
+        <v>249.214821936195</v>
       </c>
       <c r="Q33">
-        <v>255.2174837506889</v>
+        <v>254.114821936195</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08957243092125269</v>
+        <v>0.09021614314068288</v>
       </c>
       <c r="T33">
-        <v>0.853206152238044</v>
+        <v>0.8657533015356623</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.322968324654386</v>
+        <v>8.062875564508939</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07846697733566435</v>
+        <v>0.07854397733566434</v>
       </c>
       <c r="C34">
-        <v>1430.320591005919</v>
+        <v>1408.319740458686</v>
       </c>
       <c r="D34">
-        <v>2039.056629581713</v>
+        <v>2037.666280239974</v>
       </c>
       <c r="E34">
-        <v>190.5859180264376</v>
+        <v>211.1964192319311</v>
       </c>
       <c r="F34">
-        <v>659.5360385757941</v>
+        <v>680.1465397812876</v>
       </c>
       <c r="G34">
         <v>50.8</v>
@@ -4203,28 +4203,28 @@
         <v>284.5</v>
       </c>
       <c r="M34">
-        <v>35.28517806380498</v>
+        <v>36.38783987829888</v>
       </c>
       <c r="N34">
-        <v>249.214821936195</v>
+        <v>248.1121601217011</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>249.214821936195</v>
+        <v>248.1121601217011</v>
       </c>
       <c r="Q34">
-        <v>254.114821936195</v>
+        <v>253.0121601217011</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09021614314068288</v>
+        <v>0.09087907065024531</v>
       </c>
       <c r="T34">
-        <v>0.8657533015356623</v>
+        <v>0.8786749926033588</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.062875564508939</v>
+        <v>7.818546001948063</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07854397733566434</v>
+        <v>0.07889297733566436</v>
       </c>
       <c r="C35">
-        <v>1408.319740458686</v>
+        <v>1381.431225113167</v>
       </c>
       <c r="D35">
-        <v>2037.666280239974</v>
+        <v>2031.388266099949</v>
       </c>
       <c r="E35">
-        <v>211.1964192319311</v>
+        <v>231.8069204374247</v>
       </c>
       <c r="F35">
-        <v>680.1465397812876</v>
+        <v>700.7570409867812</v>
       </c>
       <c r="G35">
         <v>50.8</v>
@@ -4285,45 +4285,45 @@
         <v>284.5</v>
       </c>
       <c r="M35">
-        <v>36.38783987829888</v>
+        <v>38.05110732558222</v>
       </c>
       <c r="N35">
-        <v>248.1121601217011</v>
+        <v>246.4488926744178</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>248.1121601217011</v>
+        <v>246.4488926744178</v>
       </c>
       <c r="Q35">
-        <v>253.0121601217011</v>
+        <v>251.3488926744178</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09087907065024531</v>
+        <v>0.09156208687221873</v>
       </c>
       <c r="T35">
-        <v>0.8786749926033588</v>
+        <v>0.891988250067046</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.818546001948063</v>
+        <v>7.476786353829109</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07889297733566436</v>
+        <v>0.07897797733566436</v>
       </c>
       <c r="C36">
-        <v>1381.431225113167</v>
+        <v>1359.297548552377</v>
       </c>
       <c r="D36">
-        <v>2031.388266099949</v>
+        <v>2029.865090744652</v>
       </c>
       <c r="E36">
-        <v>231.8069204374247</v>
+        <v>252.4174216429183</v>
       </c>
       <c r="F36">
-        <v>700.7570409867812</v>
+        <v>721.3675421922749</v>
       </c>
       <c r="G36">
         <v>50.8</v>
@@ -4367,28 +4367,28 @@
         <v>284.5</v>
       </c>
       <c r="M36">
-        <v>38.05110732558222</v>
+        <v>39.17025754104053</v>
       </c>
       <c r="N36">
-        <v>246.4488926744178</v>
+        <v>245.3297424589595</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>246.4488926744178</v>
+        <v>245.3297424589595</v>
       </c>
       <c r="Q36">
-        <v>251.3488926744178</v>
+        <v>250.2297424589595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09156208687221873</v>
+        <v>0.09226611897794518</v>
       </c>
       <c r="T36">
-        <v>0.891988250067046</v>
+        <v>0.9057111462219236</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.476786353829109</v>
+        <v>7.263163886576847</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07897797733566436</v>
+        <v>0.07906297733566435</v>
       </c>
       <c r="C37">
-        <v>1359.297548552377</v>
+        <v>1337.166154494518</v>
       </c>
       <c r="D37">
-        <v>2029.865090744652</v>
+        <v>2028.344197892287</v>
       </c>
       <c r="E37">
-        <v>252.4174216429183</v>
+        <v>273.0279228484118</v>
       </c>
       <c r="F37">
-        <v>721.3675421922749</v>
+        <v>741.9780433977684</v>
       </c>
       <c r="G37">
         <v>50.8</v>
@@ -4449,28 +4449,28 @@
         <v>284.5</v>
       </c>
       <c r="M37">
-        <v>39.17025754104053</v>
+        <v>40.28940775649883</v>
       </c>
       <c r="N37">
-        <v>245.3297424589595</v>
+        <v>244.2105922435012</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>245.3297424589595</v>
+        <v>244.2105922435012</v>
       </c>
       <c r="Q37">
-        <v>250.2297424589595</v>
+        <v>249.1105922435012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09226611897794518</v>
+        <v>0.09299215208697556</v>
       </c>
       <c r="T37">
-        <v>0.9057111462219236</v>
+        <v>0.9198628828816412</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.263163886576847</v>
+        <v>7.061409334171936</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07906297733566436</v>
+        <v>0.07914797733566437</v>
       </c>
       <c r="C38">
-        <v>1337.166154494518</v>
+        <v>1315.037037812882</v>
       </c>
       <c r="D38">
-        <v>2028.344197892286</v>
+        <v>2026.825582416144</v>
       </c>
       <c r="E38">
-        <v>273.0279228484117</v>
+        <v>293.6384240539053</v>
       </c>
       <c r="F38">
-        <v>741.9780433977683</v>
+        <v>762.5885446032619</v>
       </c>
       <c r="G38">
         <v>50.8</v>
@@ -4531,28 +4531,28 @@
         <v>284.5</v>
       </c>
       <c r="M38">
-        <v>40.28940775649882</v>
+        <v>41.40855797195712</v>
       </c>
       <c r="N38">
-        <v>244.2105922435012</v>
+        <v>243.0914420280429</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>244.2105922435012</v>
+        <v>243.0914420280429</v>
       </c>
       <c r="Q38">
-        <v>249.1105922435012</v>
+        <v>247.9914420280429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09299215208697556</v>
+        <v>0.09374123386613391</v>
       </c>
       <c r="T38">
-        <v>0.9198628828816412</v>
+        <v>0.9344638810226197</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.061409334171938</v>
+        <v>6.870560433248371</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07914797733566437</v>
+        <v>0.07923297733566437</v>
       </c>
       <c r="C39">
-        <v>1315.037037812882</v>
+        <v>1292.910193396099</v>
       </c>
       <c r="D39">
-        <v>2026.825582416144</v>
+        <v>2025.309239204854</v>
       </c>
       <c r="E39">
-        <v>293.6384240539053</v>
+        <v>314.248925259399</v>
       </c>
       <c r="F39">
-        <v>762.5885446032619</v>
+        <v>783.1990458087555</v>
       </c>
       <c r="G39">
         <v>50.8</v>
@@ -4613,28 +4613,28 @@
         <v>284.5</v>
       </c>
       <c r="M39">
-        <v>41.40855797195712</v>
+        <v>42.52770818741543</v>
       </c>
       <c r="N39">
-        <v>243.0914420280429</v>
+        <v>241.9722918125846</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>243.0914420280429</v>
+        <v>241.9722918125846</v>
       </c>
       <c r="Q39">
-        <v>247.9914420280429</v>
+        <v>246.8722918125846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09374123386613391</v>
+        <v>0.09451447957365219</v>
       </c>
       <c r="T39">
-        <v>0.9344638810226197</v>
+        <v>0.9495358791036296</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.870560433248371</v>
+        <v>6.68975621132078</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07923297733566437</v>
+        <v>0.07931797733566436</v>
       </c>
       <c r="C40">
-        <v>1292.910193396099</v>
+        <v>1270.785616148086</v>
       </c>
       <c r="D40">
-        <v>2025.309239204854</v>
+        <v>2023.795163162335</v>
       </c>
       <c r="E40">
-        <v>314.248925259399</v>
+        <v>334.8594264648926</v>
       </c>
       <c r="F40">
-        <v>783.1990458087555</v>
+        <v>803.8095470142491</v>
       </c>
       <c r="G40">
         <v>50.8</v>
@@ -4695,28 +4695,28 @@
         <v>284.5</v>
       </c>
       <c r="M40">
-        <v>42.52770818741543</v>
+        <v>43.64685840287373</v>
       </c>
       <c r="N40">
-        <v>241.9722918125846</v>
+        <v>240.8531415971263</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>241.9722918125846</v>
+        <v>240.8531415971263</v>
       </c>
       <c r="Q40">
-        <v>246.8722918125846</v>
+        <v>245.7531415971263</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09451447957365219</v>
+        <v>0.09531307759944976</v>
       </c>
       <c r="T40">
-        <v>0.9495358791036296</v>
+        <v>0.9651020410561482</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.68975621132078</v>
+        <v>6.518224000774095</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07931797733566436</v>
+        <v>0.07940297733566436</v>
       </c>
       <c r="C41">
-        <v>1270.785616148086</v>
+        <v>1248.663300987987</v>
       </c>
       <c r="D41">
-        <v>2023.795163162335</v>
+        <v>2022.28334920773</v>
       </c>
       <c r="E41">
-        <v>334.8594264648926</v>
+        <v>355.4699276703861</v>
       </c>
       <c r="F41">
-        <v>803.8095470142491</v>
+        <v>824.4200482197426</v>
       </c>
       <c r="G41">
         <v>50.8</v>
@@ -4777,28 +4777,28 @@
         <v>284.5</v>
       </c>
       <c r="M41">
-        <v>43.64685840287373</v>
+        <v>44.76600861833202</v>
       </c>
       <c r="N41">
-        <v>240.8531415971263</v>
+        <v>239.733991381668</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>240.8531415971263</v>
+        <v>239.733991381668</v>
       </c>
       <c r="Q41">
-        <v>245.7531415971263</v>
+        <v>244.633991381668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09531307759944976</v>
+        <v>0.09613829555944059</v>
       </c>
       <c r="T41">
-        <v>0.9651020410561482</v>
+        <v>0.9811870750737506</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.518224000774095</v>
+        <v>6.355268400754743</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07940297733566436</v>
+        <v>0.07948797733566436</v>
       </c>
       <c r="C42">
-        <v>1248.663300987987</v>
+        <v>1226.543242850117</v>
       </c>
       <c r="D42">
-        <v>2022.28334920773</v>
+        <v>2020.773792275353</v>
       </c>
       <c r="E42">
-        <v>355.4699276703861</v>
+        <v>376.0804288758797</v>
       </c>
       <c r="F42">
-        <v>824.4200482197426</v>
+        <v>845.0305494252362</v>
       </c>
       <c r="G42">
         <v>50.8</v>
@@ -4859,28 +4859,28 @@
         <v>284.5</v>
       </c>
       <c r="M42">
-        <v>44.76600861833202</v>
+        <v>45.88515883379033</v>
       </c>
       <c r="N42">
-        <v>239.733991381668</v>
+        <v>238.6148411662097</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>239.733991381668</v>
+        <v>238.6148411662097</v>
       </c>
       <c r="Q42">
-        <v>244.633991381668</v>
+        <v>243.5148411662097</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09613829555944059</v>
+        <v>0.09699148700960061</v>
       </c>
       <c r="T42">
-        <v>0.9811870750737506</v>
+        <v>0.9978173644817802</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.355268400754743</v>
+        <v>6.200261854394871</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07948797733566436</v>
+        <v>0.07999297733566435</v>
       </c>
       <c r="C43">
-        <v>1226.543242850117</v>
+        <v>1197.010461258087</v>
       </c>
       <c r="D43">
-        <v>2020.773792275353</v>
+        <v>2011.851511888817</v>
       </c>
       <c r="E43">
-        <v>376.0804288758797</v>
+        <v>396.6909300813733</v>
       </c>
       <c r="F43">
-        <v>845.0305494252362</v>
+        <v>865.6410506307299</v>
       </c>
       <c r="G43">
         <v>50.8</v>
@@ -4941,45 +4941,45 @@
         <v>284.5</v>
       </c>
       <c r="M43">
-        <v>45.88515883379033</v>
+        <v>47.86995009987936</v>
       </c>
       <c r="N43">
-        <v>238.6148411662097</v>
+        <v>236.6300499001206</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>238.6148411662097</v>
+        <v>236.6300499001206</v>
       </c>
       <c r="Q43">
-        <v>243.5148411662097</v>
+        <v>241.5300499001206</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09699148700960061</v>
+        <v>0.09787409885459372</v>
       </c>
       <c r="T43">
-        <v>0.9978173644817802</v>
+        <v>1.015021112145259</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.200261854394871</v>
+        <v>5.943185639558814</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07999297733566436</v>
+        <v>0.08008797733566436</v>
       </c>
       <c r="C44">
-        <v>1197.010461258087</v>
+        <v>1174.730308894286</v>
       </c>
       <c r="D44">
-        <v>2011.851511888816</v>
+        <v>2010.181860730509</v>
       </c>
       <c r="E44">
-        <v>396.6909300813732</v>
+        <v>417.3014312868667</v>
       </c>
       <c r="F44">
-        <v>865.6410506307298</v>
+        <v>886.2515518362233</v>
       </c>
       <c r="G44">
         <v>50.8</v>
@@ -5023,28 +5023,28 @@
         <v>284.5</v>
       </c>
       <c r="M44">
-        <v>47.86995009987935</v>
+        <v>49.00971081654315</v>
       </c>
       <c r="N44">
-        <v>236.6300499001206</v>
+        <v>235.4902891834569</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>236.6300499001206</v>
+        <v>235.4902891834569</v>
       </c>
       <c r="Q44">
-        <v>241.5300499001206</v>
+        <v>240.3902891834569</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09787409885459372</v>
+        <v>0.09878767953625325</v>
       </c>
       <c r="T44">
-        <v>1.015021112145259</v>
+        <v>1.032828500077632</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.943185639558814</v>
+        <v>5.804972020034191</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08008797733566436</v>
+        <v>0.08018297733566437</v>
       </c>
       <c r="C45">
-        <v>1174.730308894286</v>
+        <v>1152.452925545324</v>
       </c>
       <c r="D45">
-        <v>2010.181860730509</v>
+        <v>2008.514978587041</v>
       </c>
       <c r="E45">
-        <v>417.3014312868667</v>
+        <v>437.9119324923603</v>
       </c>
       <c r="F45">
-        <v>886.2515518362233</v>
+        <v>906.8620530417169</v>
       </c>
       <c r="G45">
         <v>50.8</v>
@@ -5105,28 +5105,28 @@
         <v>284.5</v>
       </c>
       <c r="M45">
-        <v>49.00971081654315</v>
+        <v>50.14947153320694</v>
       </c>
       <c r="N45">
-        <v>235.4902891834569</v>
+        <v>234.3505284667931</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>235.4902891834569</v>
+        <v>234.3505284667931</v>
       </c>
       <c r="Q45">
-        <v>240.3902891834569</v>
+        <v>239.2505284667931</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09878767953625325</v>
+        <v>0.09973388809940065</v>
       </c>
       <c r="T45">
-        <v>1.032828500077632</v>
+        <v>1.051271866150447</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.804972020034191</v>
+        <v>5.673040837760687</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08018297733566437</v>
+        <v>0.08027797733566437</v>
       </c>
       <c r="C46">
-        <v>1152.452925545324</v>
+        <v>1130.178304328546</v>
       </c>
       <c r="D46">
-        <v>2008.514978587041</v>
+        <v>2006.850858575756</v>
       </c>
       <c r="E46">
-        <v>437.9119324923603</v>
+        <v>458.522433697854</v>
       </c>
       <c r="F46">
-        <v>906.8620530417169</v>
+        <v>927.4725542472105</v>
       </c>
       <c r="G46">
         <v>50.8</v>
@@ -5187,28 +5187,28 @@
         <v>284.5</v>
       </c>
       <c r="M46">
-        <v>50.14947153320694</v>
+        <v>51.28923224987074</v>
       </c>
       <c r="N46">
-        <v>234.3505284667931</v>
+        <v>233.2107677501293</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>234.3505284667931</v>
+        <v>233.2107677501293</v>
       </c>
       <c r="Q46">
-        <v>239.2505284667931</v>
+        <v>238.1107677501293</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09973388809940065</v>
+        <v>0.1007145042466625</v>
       </c>
       <c r="T46">
-        <v>1.051271866150447</v>
+        <v>1.070385900080455</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.673040837760687</v>
+        <v>5.546973263588226</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08027797733566437</v>
+        <v>0.08037297733566437</v>
       </c>
       <c r="C47">
-        <v>1130.178304328546</v>
+        <v>1107.906438384086</v>
       </c>
       <c r="D47">
-        <v>2006.850858575756</v>
+        <v>2005.18949383679</v>
       </c>
       <c r="E47">
-        <v>458.522433697854</v>
+        <v>479.1329349033475</v>
       </c>
       <c r="F47">
-        <v>927.4725542472105</v>
+        <v>948.083055452704</v>
       </c>
       <c r="G47">
         <v>50.8</v>
@@ -5269,28 +5269,28 @@
         <v>284.5</v>
       </c>
       <c r="M47">
-        <v>51.28923224987074</v>
+        <v>52.42899296653453</v>
       </c>
       <c r="N47">
-        <v>233.2107677501293</v>
+        <v>232.0710070334655</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>233.2107677501293</v>
+        <v>232.0710070334655</v>
       </c>
       <c r="Q47">
-        <v>238.1107677501293</v>
+        <v>236.9710070334655</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1007145042466625</v>
+        <v>0.1017314395104895</v>
       </c>
       <c r="T47">
-        <v>1.070385900080455</v>
+        <v>1.090207861193056</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.546973263588226</v>
+        <v>5.42638688829283</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08037297733566437</v>
+        <v>0.08046797733566437</v>
       </c>
       <c r="C48">
-        <v>1107.906438384086</v>
+        <v>1085.637320874774</v>
       </c>
       <c r="D48">
-        <v>2005.18949383679</v>
+        <v>2003.530877532972</v>
       </c>
       <c r="E48">
-        <v>479.1329349033475</v>
+        <v>499.7434361088411</v>
       </c>
       <c r="F48">
-        <v>948.083055452704</v>
+        <v>968.6935566581976</v>
       </c>
       <c r="G48">
         <v>50.8</v>
@@ -5351,28 +5351,28 @@
         <v>284.5</v>
       </c>
       <c r="M48">
-        <v>52.42899296653453</v>
+        <v>53.56875368319833</v>
       </c>
       <c r="N48">
-        <v>232.0710070334655</v>
+        <v>230.9312463168017</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>232.0710070334655</v>
+        <v>230.9312463168017</v>
       </c>
       <c r="Q48">
-        <v>236.9710070334655</v>
+        <v>235.8312463168017</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1017314395104895</v>
+        <v>0.1027867496899328</v>
       </c>
       <c r="T48">
-        <v>1.090207861193056</v>
+        <v>1.110777820838208</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.42638688829283</v>
+        <v>5.310931848116386</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08046797733566437</v>
+        <v>0.08056297733566437</v>
       </c>
       <c r="C49">
-        <v>1085.637320874774</v>
+        <v>1063.370944986046</v>
       </c>
       <c r="D49">
-        <v>2003.530877532972</v>
+        <v>2001.875002849737</v>
       </c>
       <c r="E49">
-        <v>499.7434361088411</v>
+        <v>520.3539373143346</v>
       </c>
       <c r="F49">
-        <v>968.6935566581976</v>
+        <v>989.3040578636912</v>
       </c>
       <c r="G49">
         <v>50.8</v>
@@ -5433,28 +5433,28 @@
         <v>284.5</v>
       </c>
       <c r="M49">
-        <v>53.56875368319833</v>
+        <v>54.70851439986212</v>
       </c>
       <c r="N49">
-        <v>230.9312463168017</v>
+        <v>229.7914856001379</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>230.9312463168017</v>
+        <v>229.7914856001379</v>
       </c>
       <c r="Q49">
-        <v>235.8312463168017</v>
+        <v>234.6914856001379</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1027867496899328</v>
+        <v>0.1038826487224315</v>
       </c>
       <c r="T49">
-        <v>1.110777820838208</v>
+        <v>1.132138932777405</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.310931848116386</v>
+        <v>5.200287434613962</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08056297733566437</v>
+        <v>0.08065797733566436</v>
       </c>
       <c r="C50">
-        <v>1063.370944986047</v>
+        <v>1041.107303925846</v>
       </c>
       <c r="D50">
-        <v>2001.875002849737</v>
+        <v>2000.221862995031</v>
       </c>
       <c r="E50">
-        <v>520.3539373143346</v>
+        <v>540.964438519828</v>
       </c>
       <c r="F50">
-        <v>989.3040578636911</v>
+        <v>1009.914559069185</v>
       </c>
       <c r="G50">
         <v>50.8</v>
@@ -5515,28 +5515,28 @@
         <v>284.5</v>
       </c>
       <c r="M50">
-        <v>54.70851439986212</v>
+        <v>55.84827511652591</v>
       </c>
       <c r="N50">
-        <v>229.7914856001379</v>
+        <v>228.6517248834741</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>229.7914856001379</v>
+        <v>228.6517248834741</v>
       </c>
       <c r="Q50">
-        <v>234.6914856001379</v>
+        <v>233.5517248834741</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1038826487224315</v>
+        <v>0.1050215241875772</v>
       </c>
       <c r="T50">
-        <v>1.132138932777405</v>
+        <v>1.154337735380883</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.200287434613963</v>
+        <v>5.094159119621841</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08065797733566436</v>
+        <v>0.08075297733566436</v>
       </c>
       <c r="C51">
-        <v>1041.107303925846</v>
+        <v>1018.846390924534</v>
       </c>
       <c r="D51">
-        <v>2000.221862995031</v>
+        <v>1998.571451199212</v>
       </c>
       <c r="E51">
-        <v>540.964438519828</v>
+        <v>561.5749397253217</v>
       </c>
       <c r="F51">
-        <v>1009.914559069185</v>
+        <v>1030.525060274678</v>
       </c>
       <c r="G51">
         <v>50.8</v>
@@ -5597,28 +5597,28 @@
         <v>284.5</v>
       </c>
       <c r="M51">
-        <v>55.84827511652591</v>
+        <v>56.98803583318971</v>
       </c>
       <c r="N51">
-        <v>228.6517248834741</v>
+        <v>227.5119641668103</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>228.6517248834741</v>
+        <v>227.5119641668103</v>
       </c>
       <c r="Q51">
-        <v>233.5517248834741</v>
+        <v>232.4119641668103</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1050215241875772</v>
+        <v>0.1062059546713287</v>
       </c>
       <c r="T51">
-        <v>1.154337735380883</v>
+        <v>1.177424490088501</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.094159119621841</v>
+        <v>4.992275937229403</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08075297733566436</v>
+        <v>0.08084797733566436</v>
       </c>
       <c r="C52">
-        <v>1018.846390924534</v>
+        <v>996.5881992347965</v>
       </c>
       <c r="D52">
-        <v>1998.571451199212</v>
+        <v>1996.923760714968</v>
       </c>
       <c r="E52">
-        <v>561.5749397253217</v>
+        <v>582.1854409308153</v>
       </c>
       <c r="F52">
-        <v>1030.525060274678</v>
+        <v>1051.135561480172</v>
       </c>
       <c r="G52">
         <v>50.8</v>
@@ -5679,28 +5679,28 @@
         <v>284.5</v>
       </c>
       <c r="M52">
-        <v>56.98803583318971</v>
+        <v>58.12779654985351</v>
       </c>
       <c r="N52">
-        <v>227.5119641668103</v>
+        <v>226.3722034501465</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>227.5119641668103</v>
+        <v>226.3722034501465</v>
       </c>
       <c r="Q52">
-        <v>232.4119641668103</v>
+        <v>231.2722034501465</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1062059546713287</v>
+        <v>0.1074387292564579</v>
       </c>
       <c r="T52">
-        <v>1.177424490088501</v>
+        <v>1.201453561314797</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.992275937229403</v>
+        <v>4.894388173754317</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08084797733566436</v>
+        <v>0.08094297733566437</v>
       </c>
       <c r="C53">
-        <v>996.5881992347965</v>
+        <v>974.3327221315512</v>
       </c>
       <c r="D53">
-        <v>1996.923760714968</v>
+        <v>1995.278784817217</v>
       </c>
       <c r="E53">
-        <v>582.1854409308153</v>
+        <v>602.7959421363089</v>
       </c>
       <c r="F53">
-        <v>1051.135561480172</v>
+        <v>1071.746062685665</v>
       </c>
       <c r="G53">
         <v>50.8</v>
@@ -5761,28 +5761,28 @@
         <v>284.5</v>
       </c>
       <c r="M53">
-        <v>58.12779654985351</v>
+        <v>59.2675572665173</v>
       </c>
       <c r="N53">
-        <v>226.3722034501465</v>
+        <v>225.2324427334827</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>226.3722034501465</v>
+        <v>225.2324427334827</v>
       </c>
       <c r="Q53">
-        <v>231.2722034501465</v>
+        <v>230.1324427334827</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1074387292564579</v>
+        <v>0.1087228694493008</v>
       </c>
       <c r="T53">
-        <v>1.201453561314797</v>
+        <v>1.226483843842188</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.894388173754317</v>
+        <v>4.800265324259041</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08094297733566437</v>
+        <v>0.08103797733566437</v>
       </c>
       <c r="C54">
-        <v>974.3327221315512</v>
+        <v>952.0799529118576</v>
       </c>
       <c r="D54">
-        <v>1995.278784817217</v>
+        <v>1993.636516803017</v>
       </c>
       <c r="E54">
-        <v>602.7959421363089</v>
+        <v>623.4064433418025</v>
       </c>
       <c r="F54">
-        <v>1071.746062685665</v>
+        <v>1092.356563891159</v>
       </c>
       <c r="G54">
         <v>50.8</v>
@@ -5843,28 +5843,28 @@
         <v>284.5</v>
       </c>
       <c r="M54">
-        <v>59.2675572665173</v>
+        <v>60.4073179831811</v>
       </c>
       <c r="N54">
-        <v>225.2324427334827</v>
+        <v>224.0926820168189</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>225.2324427334827</v>
+        <v>224.0926820168189</v>
       </c>
       <c r="Q54">
-        <v>230.1324427334827</v>
+        <v>228.9926820168189</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1087228694493008</v>
+        <v>0.1100616539056689</v>
       </c>
       <c r="T54">
-        <v>1.226483843842188</v>
+        <v>1.252579244775001</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.800265324259041</v>
+        <v>4.709694280405097</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08103797733566437</v>
+        <v>0.08113297733566437</v>
       </c>
       <c r="C55">
-        <v>952.0799529118576</v>
+        <v>929.8298848948248</v>
       </c>
       <c r="D55">
-        <v>1993.636516803017</v>
+        <v>1991.996949991477</v>
       </c>
       <c r="E55">
-        <v>623.4064433418025</v>
+        <v>644.0169445472959</v>
       </c>
       <c r="F55">
-        <v>1092.356563891159</v>
+        <v>1112.967065096653</v>
       </c>
       <c r="G55">
         <v>50.8</v>
@@ -5925,28 +5925,28 @@
         <v>284.5</v>
       </c>
       <c r="M55">
-        <v>60.4073179831811</v>
+        <v>61.54707869984489</v>
       </c>
       <c r="N55">
-        <v>224.0926820168189</v>
+        <v>222.9529213001551</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>224.0926820168189</v>
+        <v>222.9529213001551</v>
       </c>
       <c r="Q55">
-        <v>228.9926820168189</v>
+        <v>227.8529213001551</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1100616539056689</v>
+        <v>0.1114586463818791</v>
       </c>
       <c r="T55">
-        <v>1.252579244775001</v>
+        <v>1.279809228357066</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.709694280405097</v>
+        <v>4.622477719656855</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08113297733566437</v>
+        <v>0.08122797733566436</v>
       </c>
       <c r="C56">
-        <v>929.8298848948248</v>
+        <v>907.5825114215206</v>
       </c>
       <c r="D56">
-        <v>1991.996949991477</v>
+        <v>1990.360077723667</v>
       </c>
       <c r="E56">
-        <v>644.0169445472959</v>
+        <v>664.6274457527895</v>
       </c>
       <c r="F56">
-        <v>1112.967065096653</v>
+        <v>1133.577566302146</v>
       </c>
       <c r="G56">
         <v>50.8</v>
@@ -6007,28 +6007,28 @@
         <v>284.5</v>
       </c>
       <c r="M56">
-        <v>61.54707869984489</v>
+        <v>62.68683941650868</v>
       </c>
       <c r="N56">
-        <v>222.9529213001551</v>
+        <v>221.8131605834913</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>222.9529213001551</v>
+        <v>221.8131605834913</v>
       </c>
       <c r="Q56">
-        <v>227.8529213001551</v>
+        <v>226.7131605834913</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1114586463818791</v>
+        <v>0.1129177274125875</v>
       </c>
       <c r="T56">
-        <v>1.279809228357066</v>
+        <v>1.308249433431667</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.622477719656855</v>
+        <v>4.538432670208548</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08122797733566436</v>
+        <v>0.08272297733566436</v>
       </c>
       <c r="C57">
-        <v>907.5825114215206</v>
+        <v>861.5625551887433</v>
       </c>
       <c r="D57">
-        <v>1990.360077723667</v>
+        <v>1964.950622696383</v>
       </c>
       <c r="E57">
-        <v>664.6274457527895</v>
+        <v>685.2379469582831</v>
       </c>
       <c r="F57">
-        <v>1133.577566302146</v>
+        <v>1154.18806750764</v>
       </c>
       <c r="G57">
         <v>50.8</v>
@@ -6089,45 +6089,45 @@
         <v>284.5</v>
       </c>
       <c r="M57">
-        <v>62.68683941650868</v>
+        <v>66.71207030194158</v>
       </c>
       <c r="N57">
-        <v>221.8131605834913</v>
+        <v>217.7879296980584</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>221.8131605834913</v>
+        <v>217.7879296980584</v>
       </c>
       <c r="Q57">
-        <v>226.7131605834913</v>
+        <v>222.6879296980584</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1129177274125875</v>
+        <v>0.1144431303083281</v>
       </c>
       <c r="T57">
-        <v>1.308249433431667</v>
+        <v>1.337982375100569</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.538432670208548</v>
+        <v>4.264595577866812</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08272297733566436</v>
+        <v>0.08284297733566436</v>
       </c>
       <c r="C58">
-        <v>861.5625551887433</v>
+        <v>838.94059772637</v>
       </c>
       <c r="D58">
-        <v>1964.950622696383</v>
+        <v>1962.939166439503</v>
       </c>
       <c r="E58">
-        <v>685.2379469582831</v>
+        <v>705.8484481637768</v>
       </c>
       <c r="F58">
-        <v>1154.18806750764</v>
+        <v>1174.798568713133</v>
       </c>
       <c r="G58">
         <v>50.8</v>
@@ -6171,28 +6171,28 @@
         <v>284.5</v>
       </c>
       <c r="M58">
-        <v>66.71207030194158</v>
+        <v>67.90335727161911</v>
       </c>
       <c r="N58">
-        <v>217.7879296980584</v>
+        <v>216.5966427283809</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>217.7879296980584</v>
+        <v>216.5966427283809</v>
       </c>
       <c r="Q58">
-        <v>222.6879296980584</v>
+        <v>221.4966427283809</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1144431303083281</v>
+        <v>0.1160394821759636</v>
       </c>
       <c r="T58">
-        <v>1.337982375100569</v>
+        <v>1.369098244288955</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.264595577866812</v>
+        <v>4.189778111588447</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08284297733566436</v>
+        <v>0.08296297733566436</v>
       </c>
       <c r="C59">
-        <v>838.94059772637</v>
+        <v>816.3227541778501</v>
       </c>
       <c r="D59">
-        <v>1962.939166439503</v>
+        <v>1960.931824096477</v>
       </c>
       <c r="E59">
-        <v>705.8484481637768</v>
+        <v>726.4589493692704</v>
       </c>
       <c r="F59">
-        <v>1174.798568713133</v>
+        <v>1195.409069918627</v>
       </c>
       <c r="G59">
         <v>50.8</v>
@@ -6253,28 +6253,28 @@
         <v>284.5</v>
       </c>
       <c r="M59">
-        <v>67.90335727161911</v>
+        <v>69.09464424129665</v>
       </c>
       <c r="N59">
-        <v>216.5966427283809</v>
+        <v>215.4053557587034</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>216.5966427283809</v>
+        <v>215.4053557587034</v>
       </c>
       <c r="Q59">
-        <v>221.4966427283809</v>
+        <v>220.3053557587034</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1160394821759636</v>
+        <v>0.1177118507992009</v>
       </c>
       <c r="T59">
-        <v>1.369098244288955</v>
+        <v>1.40169582153393</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.189778111588447</v>
+        <v>4.11754055794037</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08296297733566435</v>
+        <v>0.08308297733566436</v>
       </c>
       <c r="C60">
-        <v>816.3227541778508</v>
+        <v>793.7090119351569</v>
       </c>
       <c r="D60">
-        <v>1960.931824096478</v>
+        <v>1958.928583059277</v>
       </c>
       <c r="E60">
-        <v>726.4589493692702</v>
+        <v>747.0694505747638</v>
       </c>
       <c r="F60">
-        <v>1195.409069918627</v>
+        <v>1216.01957112412</v>
       </c>
       <c r="G60">
         <v>50.8</v>
@@ -6335,28 +6335,28 @@
         <v>284.5</v>
       </c>
       <c r="M60">
-        <v>69.09464424129663</v>
+        <v>70.28593121097417</v>
       </c>
       <c r="N60">
-        <v>215.4053557587034</v>
+        <v>214.2140687890258</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>215.4053557587034</v>
+        <v>214.2140687890258</v>
       </c>
       <c r="Q60">
-        <v>220.3053557587034</v>
+        <v>219.1140687890258</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1177118507992008</v>
+        <v>0.1194657983796692</v>
       </c>
       <c r="T60">
-        <v>1.401695821533929</v>
+        <v>1.435883524498171</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.117540557940371</v>
+        <v>4.047751734924432</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08308297733566436</v>
+        <v>0.08530297733566436</v>
       </c>
       <c r="C61">
-        <v>793.7090119351569</v>
+        <v>736.7631193891534</v>
       </c>
       <c r="D61">
-        <v>1958.928583059277</v>
+        <v>1922.593191718767</v>
       </c>
       <c r="E61">
-        <v>747.0694505747638</v>
+        <v>767.6799517802572</v>
       </c>
       <c r="F61">
-        <v>1216.01957112412</v>
+        <v>1236.630072329614</v>
       </c>
       <c r="G61">
         <v>50.8</v>
@@ -6417,45 +6417,45 @@
         <v>284.5</v>
       </c>
       <c r="M61">
-        <v>70.28593121097417</v>
+        <v>75.80542343380533</v>
       </c>
       <c r="N61">
-        <v>214.2140687890258</v>
+        <v>208.6945765661947</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>214.2140687890258</v>
+        <v>208.6945765661947</v>
       </c>
       <c r="Q61">
-        <v>219.1140687890258</v>
+        <v>213.5945765661947</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1194657983796692</v>
+        <v>0.1213074433391609</v>
       </c>
       <c r="T61">
-        <v>1.435883524498171</v>
+        <v>1.471780612610626</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.047751734924432</v>
+        <v>3.753029626546847</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08530297733566436</v>
+        <v>0.08545797733566436</v>
       </c>
       <c r="C62">
-        <v>736.7631193891534</v>
+        <v>713.6659645931275</v>
       </c>
       <c r="D62">
-        <v>1922.593191718767</v>
+        <v>1920.106538128235</v>
       </c>
       <c r="E62">
-        <v>767.6799517802572</v>
+        <v>788.2904529857508</v>
       </c>
       <c r="F62">
-        <v>1236.630072329614</v>
+        <v>1257.240573535107</v>
       </c>
       <c r="G62">
         <v>50.8</v>
@@ -6499,28 +6499,28 @@
         <v>284.5</v>
       </c>
       <c r="M62">
-        <v>75.80542343380533</v>
+        <v>77.06884715770208</v>
       </c>
       <c r="N62">
-        <v>208.6945765661947</v>
+        <v>207.4311528422979</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>208.6945765661947</v>
+        <v>207.4311528422979</v>
       </c>
       <c r="Q62">
-        <v>213.5945765661947</v>
+        <v>212.3311528422979</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1213074433391609</v>
+        <v>0.1232435316299086</v>
       </c>
       <c r="T62">
-        <v>1.471780612610626</v>
+        <v>1.509518577036539</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.753029626546847</v>
+        <v>3.691504550701817</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08545797733566436</v>
+        <v>0.08561297733566436</v>
       </c>
       <c r="C63">
-        <v>713.6659645931275</v>
+        <v>690.5752338902055</v>
       </c>
       <c r="D63">
-        <v>1920.106538128235</v>
+        <v>1917.626308630807</v>
       </c>
       <c r="E63">
-        <v>788.2904529857508</v>
+        <v>808.9009541912444</v>
       </c>
       <c r="F63">
-        <v>1257.240573535107</v>
+        <v>1277.851074740601</v>
       </c>
       <c r="G63">
         <v>50.8</v>
@@ -6581,28 +6581,28 @@
         <v>284.5</v>
       </c>
       <c r="M63">
-        <v>77.06884715770208</v>
+        <v>78.33227088159884</v>
       </c>
       <c r="N63">
-        <v>207.4311528422979</v>
+        <v>206.1677291184012</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>207.4311528422979</v>
+        <v>206.1677291184012</v>
       </c>
       <c r="Q63">
-        <v>212.3311528422979</v>
+        <v>211.0677291184012</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1232435316299086</v>
+        <v>0.1252815193043799</v>
       </c>
       <c r="T63">
-        <v>1.509518577036539</v>
+        <v>1.549242750116448</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.691504550701817</v>
+        <v>3.631964154722755</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08561297733566436</v>
+        <v>0.08576797733566435</v>
       </c>
       <c r="C64">
-        <v>690.5752338902055</v>
+        <v>667.4909024182195</v>
       </c>
       <c r="D64">
-        <v>1917.626308630807</v>
+        <v>1915.152478364314</v>
       </c>
       <c r="E64">
-        <v>808.9009541912444</v>
+        <v>829.511455396738</v>
       </c>
       <c r="F64">
-        <v>1277.851074740601</v>
+        <v>1298.461575946095</v>
       </c>
       <c r="G64">
         <v>50.8</v>
@@ -6663,28 +6663,28 @@
         <v>284.5</v>
       </c>
       <c r="M64">
-        <v>78.33227088159884</v>
+        <v>79.59569460549559</v>
       </c>
       <c r="N64">
-        <v>206.1677291184012</v>
+        <v>204.9043053945044</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>206.1677291184012</v>
+        <v>204.9043053945044</v>
       </c>
       <c r="Q64">
-        <v>211.0677291184012</v>
+        <v>209.8043053945044</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1252815193043799</v>
+        <v>0.1274296684747685</v>
       </c>
       <c r="T64">
-        <v>1.549242750116448</v>
+        <v>1.591114175795271</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.631964154722755</v>
+        <v>3.574313930044616</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08576797733566435</v>
+        <v>0.08592297733566437</v>
       </c>
       <c r="C65">
-        <v>667.4909024182195</v>
+        <v>644.4129454431286</v>
       </c>
       <c r="D65">
-        <v>1915.152478364314</v>
+        <v>1912.685022594717</v>
       </c>
       <c r="E65">
-        <v>829.511455396738</v>
+        <v>850.1219566022316</v>
       </c>
       <c r="F65">
-        <v>1298.461575946095</v>
+        <v>1319.072077151588</v>
       </c>
       <c r="G65">
         <v>50.8</v>
@@ -6745,28 +6745,28 @@
         <v>284.5</v>
       </c>
       <c r="M65">
-        <v>79.59569460549559</v>
+        <v>80.85911832939236</v>
       </c>
       <c r="N65">
-        <v>204.9043053945044</v>
+        <v>203.6408816706077</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>204.9043053945044</v>
+        <v>203.6408816706077</v>
       </c>
       <c r="Q65">
-        <v>209.8043053945044</v>
+        <v>208.5408816706077</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1274296684747685</v>
+        <v>0.1296971592657343</v>
       </c>
       <c r="T65">
-        <v>1.591114175795271</v>
+        <v>1.635311791789584</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.574313930044616</v>
+        <v>3.518465274887669</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08592297733566437</v>
+        <v>0.08789797733566437</v>
       </c>
       <c r="C66">
-        <v>644.4129454431286</v>
+        <v>592.9099369185587</v>
       </c>
       <c r="D66">
-        <v>1912.685022594717</v>
+        <v>1881.792515275641</v>
       </c>
       <c r="E66">
-        <v>850.1219566022316</v>
+        <v>870.7324578077253</v>
       </c>
       <c r="F66">
-        <v>1319.072077151588</v>
+        <v>1339.682578357082</v>
       </c>
       <c r="G66">
         <v>50.8</v>
@@ -6827,45 +6827,45 @@
         <v>284.5</v>
       </c>
       <c r="M66">
-        <v>80.85911832939236</v>
+        <v>85.87365327268895</v>
       </c>
       <c r="N66">
-        <v>203.6408816706077</v>
+        <v>198.626346727311</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>203.6408816706077</v>
+        <v>198.626346727311</v>
       </c>
       <c r="Q66">
-        <v>208.5408816706077</v>
+        <v>203.5263467273111</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1296971592657343</v>
+        <v>0.1320942209590411</v>
       </c>
       <c r="T66">
-        <v>1.635311791789584</v>
+        <v>1.682034985840716</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.518465274887669</v>
+        <v>3.313006832218721</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08789797733566437</v>
+        <v>0.08808097733566436</v>
       </c>
       <c r="C67">
-        <v>592.9099369185587</v>
+        <v>569.487431503494</v>
       </c>
       <c r="D67">
-        <v>1881.792515275641</v>
+        <v>1878.980511066069</v>
       </c>
       <c r="E67">
-        <v>870.7324578077253</v>
+        <v>891.3429590132187</v>
       </c>
       <c r="F67">
-        <v>1339.682578357082</v>
+        <v>1360.293079562575</v>
       </c>
       <c r="G67">
         <v>50.8</v>
@@ -6909,28 +6909,28 @@
         <v>284.5</v>
       </c>
       <c r="M67">
-        <v>85.87365327268895</v>
+        <v>87.19478639996107</v>
       </c>
       <c r="N67">
-        <v>198.626346727311</v>
+        <v>197.3052136000389</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>198.626346727311</v>
+        <v>197.3052136000389</v>
       </c>
       <c r="Q67">
-        <v>203.5263467273111</v>
+        <v>202.2052136000389</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1320942209590411</v>
+        <v>0.1346322862813658</v>
       </c>
       <c r="T67">
-        <v>1.682034985840716</v>
+        <v>1.731506603071325</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.313006832218721</v>
+        <v>3.262809759003286</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08808097733566436</v>
+        <v>0.08826397733566435</v>
       </c>
       <c r="C68">
-        <v>569.487431503494</v>
+        <v>546.0733176290339</v>
       </c>
       <c r="D68">
-        <v>1878.980511066069</v>
+        <v>1876.176898397103</v>
       </c>
       <c r="E68">
-        <v>891.3429590132187</v>
+        <v>911.9534602187123</v>
       </c>
       <c r="F68">
-        <v>1360.293079562575</v>
+        <v>1380.903580768069</v>
       </c>
       <c r="G68">
         <v>50.8</v>
@@ -6991,28 +6991,28 @@
         <v>284.5</v>
       </c>
       <c r="M68">
-        <v>87.19478639996107</v>
+        <v>88.51591952723322</v>
       </c>
       <c r="N68">
-        <v>197.3052136000389</v>
+        <v>195.9840804727668</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>197.3052136000389</v>
+        <v>195.9840804727668</v>
       </c>
       <c r="Q68">
-        <v>202.2052136000389</v>
+        <v>200.8840804727668</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1346322862813658</v>
+        <v>0.1373241737444374</v>
       </c>
       <c r="T68">
-        <v>1.731506603071325</v>
+        <v>1.783976500134092</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.262809759003286</v>
+        <v>3.214111105883834</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08826397733566435</v>
+        <v>0.08844697733566437</v>
       </c>
       <c r="C69">
-        <v>546.0733176290339</v>
+        <v>522.6675577882786</v>
       </c>
       <c r="D69">
-        <v>1876.176898397103</v>
+        <v>1873.381639761841</v>
       </c>
       <c r="E69">
-        <v>911.9534602187123</v>
+        <v>932.5639614242059</v>
       </c>
       <c r="F69">
-        <v>1380.903580768069</v>
+        <v>1401.514081973562</v>
       </c>
       <c r="G69">
         <v>50.8</v>
@@ -7073,28 +7073,28 @@
         <v>284.5</v>
       </c>
       <c r="M69">
-        <v>88.51591952723322</v>
+        <v>89.83705265450536</v>
       </c>
       <c r="N69">
-        <v>195.9840804727668</v>
+        <v>194.6629473454946</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>195.9840804727668</v>
+        <v>194.6629473454946</v>
       </c>
       <c r="Q69">
-        <v>200.8840804727668</v>
+        <v>199.5629473454946</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1373241737444374</v>
+        <v>0.1401843041739511</v>
       </c>
       <c r="T69">
-        <v>1.783976500134092</v>
+        <v>1.839725765763283</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.214111105883834</v>
+        <v>3.166844766091424</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08844697733566437</v>
+        <v>0.08862997733566436</v>
       </c>
       <c r="C70">
-        <v>522.6675577882786</v>
+        <v>499.2701146975173</v>
       </c>
       <c r="D70">
-        <v>1873.381639761841</v>
+        <v>1870.594697876573</v>
       </c>
       <c r="E70">
-        <v>932.5639614242059</v>
+        <v>953.1744626296995</v>
       </c>
       <c r="F70">
-        <v>1401.514081973562</v>
+        <v>1422.124583179056</v>
       </c>
       <c r="G70">
         <v>50.8</v>
@@ -7155,28 +7155,28 @@
         <v>284.5</v>
       </c>
       <c r="M70">
-        <v>89.83705265450536</v>
+        <v>91.1581857817775</v>
       </c>
       <c r="N70">
-        <v>194.6629473454946</v>
+        <v>193.3418142182225</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>194.6629473454946</v>
+        <v>193.3418142182225</v>
       </c>
       <c r="Q70">
-        <v>199.5629473454946</v>
+        <v>198.2418142182225</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1401843041739511</v>
+        <v>0.1432289591473044</v>
       </c>
       <c r="T70">
-        <v>1.839725765763283</v>
+        <v>1.89907175820726</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.166844766091424</v>
+        <v>3.120948465133578</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08862997733566436</v>
+        <v>0.08881297733566437</v>
       </c>
       <c r="C71">
-        <v>499.2701146975173</v>
+        <v>475.8809512945709</v>
       </c>
       <c r="D71">
-        <v>1870.594697876573</v>
+        <v>1867.816035679121</v>
       </c>
       <c r="E71">
-        <v>953.1744626296995</v>
+        <v>973.7849638351931</v>
       </c>
       <c r="F71">
-        <v>1422.124583179056</v>
+        <v>1442.73508438455</v>
       </c>
       <c r="G71">
         <v>50.8</v>
@@ -7237,28 +7237,28 @@
         <v>284.5</v>
       </c>
       <c r="M71">
-        <v>91.1581857817775</v>
+        <v>92.47931890904964</v>
       </c>
       <c r="N71">
-        <v>193.3418142182225</v>
+        <v>192.0206810909503</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>193.3418142182225</v>
+        <v>192.0206810909503</v>
       </c>
       <c r="Q71">
-        <v>198.2418142182225</v>
+        <v>196.9206810909504</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1432289591473044</v>
+        <v>0.1464765911188812</v>
       </c>
       <c r="T71">
-        <v>1.89907175820726</v>
+        <v>1.962374150147502</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.120948465133578</v>
+        <v>3.076363487060241</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08881297733566437</v>
+        <v>0.08899597733566436</v>
       </c>
       <c r="C72">
-        <v>475.8809512945709</v>
+        <v>452.5000307371481</v>
       </c>
       <c r="D72">
-        <v>1867.816035679121</v>
+        <v>1865.045616327192</v>
       </c>
       <c r="E72">
-        <v>973.7849638351931</v>
+        <v>994.3954650406868</v>
       </c>
       <c r="F72">
-        <v>1442.73508438455</v>
+        <v>1463.345585590043</v>
       </c>
       <c r="G72">
         <v>50.8</v>
@@ -7319,28 +7319,28 @@
         <v>284.5</v>
       </c>
       <c r="M72">
-        <v>92.47931890904964</v>
+        <v>93.80045203632179</v>
       </c>
       <c r="N72">
-        <v>192.0206810909503</v>
+        <v>190.6995479636782</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>192.0206810909503</v>
+        <v>190.6995479636782</v>
       </c>
       <c r="Q72">
-        <v>196.9206810909504</v>
+        <v>195.5995479636782</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1464765911188812</v>
+        <v>0.1499481977091875</v>
       </c>
       <c r="T72">
-        <v>1.962374150147502</v>
+        <v>2.030042224290519</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.076363487060241</v>
+        <v>3.033034423862209</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08899597733566436</v>
+        <v>0.09479497733566436</v>
       </c>
       <c r="C73">
-        <v>452.5000307371483</v>
+        <v>348.1644614641771</v>
       </c>
       <c r="D73">
-        <v>1865.045616327192</v>
+        <v>1781.320548259714</v>
       </c>
       <c r="E73">
-        <v>994.3954650406865</v>
+        <v>1015.00596624618</v>
       </c>
       <c r="F73">
-        <v>1463.345585590043</v>
+        <v>1483.956086795537</v>
       </c>
       <c r="G73">
         <v>50.8</v>
@@ -7401,45 +7401,45 @@
         <v>284.5</v>
       </c>
       <c r="M73">
-        <v>93.80045203632177</v>
+        <v>106.6964426405991</v>
       </c>
       <c r="N73">
-        <v>190.6995479636782</v>
+        <v>177.8035573594009</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>190.6995479636782</v>
+        <v>177.8035573594009</v>
       </c>
       <c r="Q73">
-        <v>195.5995479636782</v>
+        <v>182.7035573594009</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1499481977091874</v>
+        <v>0.1536677761988013</v>
       </c>
       <c r="T73">
-        <v>2.030042224290519</v>
+        <v>2.102543732300894</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.03303442386221</v>
+        <v>2.666443163042671</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09479497733566436</v>
+        <v>0.09505597733566437</v>
       </c>
       <c r="C74">
-        <v>348.1644614641771</v>
+        <v>323.9621041420739</v>
       </c>
       <c r="D74">
-        <v>1781.320548259714</v>
+        <v>1777.728692143104</v>
       </c>
       <c r="E74">
-        <v>1015.00596624618</v>
+        <v>1035.616467451674</v>
       </c>
       <c r="F74">
-        <v>1483.956086795537</v>
+        <v>1504.56658800103</v>
       </c>
       <c r="G74">
         <v>50.8</v>
@@ -7483,28 +7483,28 @@
         <v>284.5</v>
       </c>
       <c r="M74">
-        <v>106.6964426405991</v>
+        <v>108.1783376772741</v>
       </c>
       <c r="N74">
-        <v>177.8035573594009</v>
+        <v>176.3216623227259</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>177.8035573594009</v>
+        <v>176.3216623227259</v>
       </c>
       <c r="Q74">
-        <v>182.7035573594009</v>
+        <v>181.2216623227259</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1536677761988013</v>
+        <v>0.1576628790209791</v>
       </c>
       <c r="T74">
-        <v>2.102543732300894</v>
+        <v>2.180415722386112</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.666443163042671</v>
+        <v>2.629916544370854</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09505597733566437</v>
+        <v>0.09531697733566437</v>
       </c>
       <c r="C75">
-        <v>323.9621041420739</v>
+        <v>299.7742029135372</v>
       </c>
       <c r="D75">
-        <v>1777.728692143104</v>
+        <v>1774.151292120061</v>
       </c>
       <c r="E75">
-        <v>1035.616467451674</v>
+        <v>1056.226968657167</v>
       </c>
       <c r="F75">
-        <v>1504.56658800103</v>
+        <v>1525.177089206524</v>
       </c>
       <c r="G75">
         <v>50.8</v>
@@ -7565,28 +7565,28 @@
         <v>284.5</v>
       </c>
       <c r="M75">
-        <v>108.1783376772741</v>
+        <v>109.6602327139491</v>
       </c>
       <c r="N75">
-        <v>176.3216623227259</v>
+        <v>174.8397672860509</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>176.3216623227259</v>
+        <v>174.8397672860509</v>
       </c>
       <c r="Q75">
-        <v>181.2216623227259</v>
+        <v>179.7397672860509</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1576628790209791</v>
+        <v>0.1619652974448629</v>
       </c>
       <c r="T75">
-        <v>2.180415722386112</v>
+        <v>2.264277865554809</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.629916544370854</v>
+        <v>2.594377131609085</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09531697733566437</v>
+        <v>0.09557797733566437</v>
       </c>
       <c r="C76">
-        <v>299.7742029135372</v>
+        <v>275.6006706819751</v>
       </c>
       <c r="D76">
-        <v>1774.151292120061</v>
+        <v>1770.588261093993</v>
       </c>
       <c r="E76">
-        <v>1056.226968657167</v>
+        <v>1076.837469862661</v>
       </c>
       <c r="F76">
-        <v>1525.177089206524</v>
+        <v>1545.787590412017</v>
       </c>
       <c r="G76">
         <v>50.8</v>
@@ -7647,28 +7647,28 @@
         <v>284.5</v>
       </c>
       <c r="M76">
-        <v>109.6602327139491</v>
+        <v>111.1421277506241</v>
       </c>
       <c r="N76">
-        <v>174.8397672860509</v>
+        <v>173.3578722493759</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>174.8397672860509</v>
+        <v>173.3578722493759</v>
       </c>
       <c r="Q76">
-        <v>179.7397672860509</v>
+        <v>178.2578722493759</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1619652974448629</v>
+        <v>0.1666119093426574</v>
       </c>
       <c r="T76">
-        <v>2.264277865554809</v>
+        <v>2.354848980177001</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.594377131609085</v>
+        <v>2.559785436520964</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09557797733566437</v>
+        <v>0.09583897733566438</v>
       </c>
       <c r="C77">
-        <v>275.6006706819751</v>
+        <v>251.4414210490595</v>
       </c>
       <c r="D77">
-        <v>1770.588261093993</v>
+        <v>1767.039512666571</v>
       </c>
       <c r="E77">
-        <v>1076.837469862661</v>
+        <v>1097.447971068154</v>
       </c>
       <c r="F77">
-        <v>1545.787590412017</v>
+        <v>1566.398091617511</v>
       </c>
       <c r="G77">
         <v>50.8</v>
@@ -7729,28 +7729,28 @@
         <v>284.5</v>
       </c>
       <c r="M77">
-        <v>111.1421277506241</v>
+        <v>112.6240227872991</v>
       </c>
       <c r="N77">
-        <v>173.3578722493759</v>
+        <v>171.8759772127009</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>173.3578722493759</v>
+        <v>171.8759772127009</v>
       </c>
       <c r="Q77">
-        <v>178.2578722493759</v>
+        <v>176.775977212701</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1666119093426574</v>
+        <v>0.1716457388986015</v>
       </c>
       <c r="T77">
-        <v>2.354848980177001</v>
+        <v>2.452967687684377</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.559785436520964</v>
+        <v>2.52610404919832</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09583897733566438</v>
+        <v>0.09910297733566437</v>
       </c>
       <c r="C78">
-        <v>251.4414210490595</v>
+        <v>187.6231210799708</v>
       </c>
       <c r="D78">
-        <v>1767.039512666571</v>
+        <v>1723.831713902975</v>
       </c>
       <c r="E78">
-        <v>1097.447971068154</v>
+        <v>1118.058472273648</v>
       </c>
       <c r="F78">
-        <v>1566.398091617511</v>
+        <v>1587.008592823005</v>
       </c>
       <c r="G78">
         <v>50.8</v>
@@ -7811,45 +7811,45 @@
         <v>284.5</v>
       </c>
       <c r="M78">
-        <v>112.6240227872991</v>
+        <v>120.2952513359838</v>
       </c>
       <c r="N78">
-        <v>171.8759772127009</v>
+        <v>164.2047486640162</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>171.8759772127009</v>
+        <v>164.2047486640162</v>
       </c>
       <c r="Q78">
-        <v>176.775977212701</v>
+        <v>169.1047486640162</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1716457388986015</v>
+        <v>0.1771172927637581</v>
       </c>
       <c r="T78">
-        <v>2.452967687684377</v>
+        <v>2.559618456714132</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.52610404919832</v>
+        <v>2.36501438619047</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09910297733566437</v>
+        <v>0.09940297733566436</v>
       </c>
       <c r="C79">
-        <v>187.6231210799708</v>
+        <v>163.1471090070279</v>
       </c>
       <c r="D79">
-        <v>1723.831713902975</v>
+        <v>1719.966203035526</v>
       </c>
       <c r="E79">
-        <v>1118.058472273648</v>
+        <v>1138.668973479142</v>
       </c>
       <c r="F79">
-        <v>1587.008592823005</v>
+        <v>1607.619094028498</v>
       </c>
       <c r="G79">
         <v>50.8</v>
@@ -7893,28 +7893,28 @@
         <v>284.5</v>
       </c>
       <c r="M79">
-        <v>120.2952513359838</v>
+        <v>121.8575273273602</v>
       </c>
       <c r="N79">
-        <v>164.2047486640162</v>
+        <v>162.6424726726398</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>164.2047486640162</v>
+        <v>162.6424726726398</v>
       </c>
       <c r="Q79">
-        <v>169.1047486640162</v>
+        <v>167.5424726726398</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1771172927637581</v>
+        <v>0.1830862606166562</v>
       </c>
       <c r="T79">
-        <v>2.559618456714132</v>
+        <v>2.675964750201138</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.36501438619047</v>
+        <v>2.334693688931618</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09940297733566436</v>
+        <v>0.09970297733566436</v>
       </c>
       <c r="C80">
-        <v>163.1471090070279</v>
+        <v>138.6883941480326</v>
       </c>
       <c r="D80">
-        <v>1719.966203035526</v>
+        <v>1716.117989382024</v>
       </c>
       <c r="E80">
-        <v>1138.668973479142</v>
+        <v>1159.279474684635</v>
       </c>
       <c r="F80">
-        <v>1607.619094028498</v>
+        <v>1628.229595233992</v>
       </c>
       <c r="G80">
         <v>50.8</v>
@@ -7975,28 +7975,28 @@
         <v>284.5</v>
       </c>
       <c r="M80">
-        <v>121.8575273273602</v>
+        <v>123.4198033187366</v>
       </c>
       <c r="N80">
-        <v>162.6424726726398</v>
+        <v>161.0801966812634</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>162.6424726726398</v>
+        <v>161.0801966812634</v>
       </c>
       <c r="Q80">
-        <v>167.5424726726398</v>
+        <v>165.9801966812634</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1830862606166562</v>
+        <v>0.1896237015984018</v>
       </c>
       <c r="T80">
-        <v>2.675964750201138</v>
+        <v>2.803391643067859</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.334693688931618</v>
+        <v>2.305140604261598</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09970297733566436</v>
+        <v>0.1000029773356644</v>
       </c>
       <c r="C81">
-        <v>138.6883941480326</v>
+        <v>114.246860660975</v>
       </c>
       <c r="D81">
-        <v>1716.117989382024</v>
+        <v>1712.28695710046</v>
       </c>
       <c r="E81">
-        <v>1159.279474684635</v>
+        <v>1179.889975890129</v>
       </c>
       <c r="F81">
-        <v>1628.229595233992</v>
+        <v>1648.840096439485</v>
       </c>
       <c r="G81">
         <v>50.8</v>
@@ -8057,28 +8057,28 @@
         <v>284.5</v>
       </c>
       <c r="M81">
-        <v>123.4198033187366</v>
+        <v>124.982079310113</v>
       </c>
       <c r="N81">
-        <v>161.0801966812634</v>
+        <v>159.517920689887</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>161.0801966812634</v>
+        <v>159.517920689887</v>
       </c>
       <c r="Q81">
-        <v>165.9801966812634</v>
+        <v>164.417920689887</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1896237015984018</v>
+        <v>0.1968148866783218</v>
       </c>
       <c r="T81">
-        <v>2.803391643067859</v>
+        <v>2.943561225221252</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.305140604261598</v>
+        <v>2.276326346708328</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1000029773356644</v>
+        <v>0.1003029773356644</v>
       </c>
       <c r="C82">
-        <v>114.246860660975</v>
+        <v>89.82239373595826</v>
       </c>
       <c r="D82">
-        <v>1712.28695710046</v>
+        <v>1708.472991380937</v>
       </c>
       <c r="E82">
-        <v>1179.889975890129</v>
+        <v>1200.500477095622</v>
       </c>
       <c r="F82">
-        <v>1648.840096439485</v>
+        <v>1669.450597644979</v>
       </c>
       <c r="G82">
         <v>50.8</v>
@@ -8139,28 +8139,28 @@
         <v>284.5</v>
       </c>
       <c r="M82">
-        <v>124.982079310113</v>
+        <v>126.5443553014894</v>
       </c>
       <c r="N82">
-        <v>159.517920689887</v>
+        <v>157.9556446985106</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>159.517920689887</v>
+        <v>157.9556446985106</v>
       </c>
       <c r="Q82">
-        <v>164.417920689887</v>
+        <v>162.8556446985106</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1968148866783218</v>
+        <v>0.2047630386087598</v>
       </c>
       <c r="T82">
-        <v>2.943561225221252</v>
+        <v>3.098485500232897</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.276326346708328</v>
+        <v>2.248223552304522</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1003029773356644</v>
+        <v>0.1006029773356644</v>
       </c>
       <c r="C83">
-        <v>89.82239373595826</v>
+        <v>65.41487958372568</v>
       </c>
       <c r="D83">
-        <v>1708.472991380937</v>
+        <v>1704.675978434198</v>
       </c>
       <c r="E83">
-        <v>1200.500477095622</v>
+        <v>1221.110978301116</v>
       </c>
       <c r="F83">
-        <v>1669.450597644979</v>
+        <v>1690.061098850472</v>
       </c>
       <c r="G83">
         <v>50.8</v>
@@ -8221,28 +8221,28 @@
         <v>284.5</v>
       </c>
       <c r="M83">
-        <v>126.5443553014894</v>
+        <v>128.1066312928658</v>
       </c>
       <c r="N83">
-        <v>157.9556446985106</v>
+        <v>156.3933687071342</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>157.9556446985106</v>
+        <v>156.3933687071342</v>
       </c>
       <c r="Q83">
-        <v>162.8556446985106</v>
+        <v>161.2933687071342</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2047630386087598</v>
+        <v>0.2135943185314687</v>
       </c>
       <c r="T83">
-        <v>3.098485500232897</v>
+        <v>3.270623583579169</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.248223552304522</v>
+        <v>2.220806191910564</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1006029773356644</v>
+        <v>0.1009029773356644</v>
       </c>
       <c r="C84">
-        <v>65.41487958372568</v>
+        <v>41.02420542434606</v>
       </c>
       <c r="D84">
-        <v>1704.675978434198</v>
+        <v>1700.895805480312</v>
       </c>
       <c r="E84">
-        <v>1221.110978301116</v>
+        <v>1241.72147950661</v>
       </c>
       <c r="F84">
-        <v>1690.061098850472</v>
+        <v>1710.671600055966</v>
       </c>
       <c r="G84">
         <v>50.8</v>
@@ -8303,28 +8303,28 @@
         <v>284.5</v>
       </c>
       <c r="M84">
-        <v>128.1066312928658</v>
+        <v>129.6689072842422</v>
       </c>
       <c r="N84">
-        <v>156.3933687071342</v>
+        <v>154.8310927157578</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>156.3933687071342</v>
+        <v>154.8310927157578</v>
       </c>
       <c r="Q84">
-        <v>161.2933687071342</v>
+        <v>159.7310927157578</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2135943185314687</v>
+        <v>0.2234645725627316</v>
       </c>
       <c r="T84">
-        <v>3.270623583579169</v>
+        <v>3.46301320614265</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.220806191910564</v>
+        <v>2.194049490803208</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1009029773356644</v>
+        <v>0.1012029773356644</v>
       </c>
       <c r="C85">
-        <v>41.02420542434606</v>
+        <v>16.65025947604727</v>
       </c>
       <c r="D85">
-        <v>1700.895805480312</v>
+        <v>1697.132360737507</v>
       </c>
       <c r="E85">
-        <v>1241.72147950661</v>
+        <v>1262.331980712103</v>
       </c>
       <c r="F85">
-        <v>1710.671600055966</v>
+        <v>1731.28210126146</v>
       </c>
       <c r="G85">
         <v>50.8</v>
@@ -8385,28 +8385,28 @@
         <v>284.5</v>
       </c>
       <c r="M85">
-        <v>129.6689072842422</v>
+        <v>131.2311832756187</v>
       </c>
       <c r="N85">
-        <v>154.8310927157578</v>
+        <v>153.2688167243813</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>154.8310927157578</v>
+        <v>153.2688167243813</v>
       </c>
       <c r="Q85">
-        <v>159.7310927157578</v>
+        <v>158.1688167243813</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2234645725627316</v>
+        <v>0.2345686083479024</v>
       </c>
       <c r="T85">
-        <v>3.46301320614265</v>
+        <v>3.679451531526567</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.194049490803208</v>
+        <v>2.167929854007931</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1012029773356644</v>
+        <v>0.1015029773356644</v>
       </c>
       <c r="C86">
-        <v>16.65025947604749</v>
+        <v>-7.707069055802094</v>
       </c>
       <c r="D86">
-        <v>1697.132360737507</v>
+        <v>1693.385533411151</v>
       </c>
       <c r="E86">
-        <v>1262.331980712103</v>
+        <v>1282.942481917596</v>
       </c>
       <c r="F86">
-        <v>1731.28210126146</v>
+        <v>1751.892602466953</v>
       </c>
       <c r="G86">
         <v>50.8</v>
@@ -8467,28 +8467,28 @@
         <v>284.5</v>
       </c>
       <c r="M86">
-        <v>131.2311832756186</v>
+        <v>132.793459266995</v>
       </c>
       <c r="N86">
-        <v>153.2688167243814</v>
+        <v>151.706540733005</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>153.2688167243814</v>
+        <v>151.706540733005</v>
       </c>
       <c r="Q86">
-        <v>158.1688167243814</v>
+        <v>156.606540733005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2345686083479022</v>
+        <v>0.2471531822377624</v>
       </c>
       <c r="T86">
-        <v>3.679451531526564</v>
+        <v>3.924748300295002</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.167929854007931</v>
+        <v>2.142424796901956</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1015029773356644</v>
+        <v>0.1018029773356644</v>
       </c>
       <c r="C87">
-        <v>-7.707069055802094</v>
+        <v>-32.04788998956769</v>
       </c>
       <c r="D87">
-        <v>1693.385533411151</v>
+        <v>1689.655213682879</v>
       </c>
       <c r="E87">
-        <v>1282.942481917596</v>
+        <v>1303.55298312309</v>
       </c>
       <c r="F87">
-        <v>1751.892602466953</v>
+        <v>1772.503103672447</v>
       </c>
       <c r="G87">
         <v>50.8</v>
@@ -8549,28 +8549,28 @@
         <v>284.5</v>
       </c>
       <c r="M87">
-        <v>132.793459266995</v>
+        <v>134.3557352583715</v>
       </c>
       <c r="N87">
-        <v>151.706540733005</v>
+        <v>150.1442647416285</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>151.706540733005</v>
+        <v>150.1442647416285</v>
       </c>
       <c r="Q87">
-        <v>156.606540733005</v>
+        <v>155.0442647416286</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2471531822377624</v>
+        <v>0.2615355523976026</v>
       </c>
       <c r="T87">
-        <v>3.924748300295002</v>
+        <v>4.205087464601788</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.142424796901956</v>
+        <v>2.11751288065891</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1018029773356644</v>
+        <v>0.1021029773356644</v>
       </c>
       <c r="C88">
-        <v>-32.04788998956769</v>
+        <v>-56.37231217807403</v>
       </c>
       <c r="D88">
-        <v>1689.655213682879</v>
+        <v>1685.941292699866</v>
       </c>
       <c r="E88">
-        <v>1303.55298312309</v>
+        <v>1324.163484328584</v>
       </c>
       <c r="F88">
-        <v>1772.503103672447</v>
+        <v>1793.11360487794</v>
       </c>
       <c r="G88">
         <v>50.8</v>
@@ -8631,28 +8631,28 @@
         <v>284.5</v>
       </c>
       <c r="M88">
-        <v>134.3557352583715</v>
+        <v>135.9180112497479</v>
       </c>
       <c r="N88">
-        <v>150.1442647416285</v>
+        <v>148.5819887502521</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>150.1442647416285</v>
+        <v>148.5819887502521</v>
       </c>
       <c r="Q88">
-        <v>155.0442647416286</v>
+        <v>153.4819887502521</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2615355523976026</v>
+        <v>0.2781305948897259</v>
       </c>
       <c r="T88">
-        <v>4.205087464601788</v>
+        <v>4.528555731109618</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.11751288065891</v>
+        <v>2.093173652145589</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1021029773356644</v>
+        <v>0.1024029773356644</v>
       </c>
       <c r="C89">
-        <v>-56.37231217807403</v>
+        <v>-80.68044351919752</v>
       </c>
       <c r="D89">
-        <v>1685.941292699866</v>
+        <v>1682.243662564236</v>
       </c>
       <c r="E89">
-        <v>1324.163484328584</v>
+        <v>1344.773985534077</v>
       </c>
       <c r="F89">
-        <v>1793.11360487794</v>
+        <v>1813.724106083434</v>
       </c>
       <c r="G89">
         <v>50.8</v>
@@ -8713,28 +8713,28 @@
         <v>284.5</v>
       </c>
       <c r="M89">
-        <v>135.9180112497479</v>
+        <v>137.4802872411243</v>
       </c>
       <c r="N89">
-        <v>148.5819887502521</v>
+        <v>147.0197127588757</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>148.5819887502521</v>
+        <v>147.0197127588757</v>
       </c>
       <c r="Q89">
-        <v>153.4819887502521</v>
+        <v>151.9197127588757</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2781305948897259</v>
+        <v>0.297491477797203</v>
       </c>
       <c r="T89">
-        <v>4.528555731109618</v>
+        <v>4.905935375368753</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.093173652145589</v>
+        <v>2.069387587916662</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1024029773356644</v>
+        <v>0.1027029773356644</v>
       </c>
       <c r="C90">
-        <v>-80.68044351919752</v>
+        <v>-104.9723909663123</v>
       </c>
       <c r="D90">
-        <v>1682.243662564236</v>
+        <v>1678.562216322615</v>
       </c>
       <c r="E90">
-        <v>1344.773985534077</v>
+        <v>1365.384486739571</v>
       </c>
       <c r="F90">
-        <v>1813.724106083434</v>
+        <v>1834.334607288927</v>
       </c>
       <c r="G90">
         <v>50.8</v>
@@ -8795,28 +8795,28 @@
         <v>284.5</v>
       </c>
       <c r="M90">
-        <v>137.4802872411243</v>
+        <v>139.0425632325007</v>
       </c>
       <c r="N90">
-        <v>147.0197127588757</v>
+        <v>145.4574367674993</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>147.0197127588757</v>
+        <v>145.4574367674993</v>
       </c>
       <c r="Q90">
-        <v>151.9197127588757</v>
+        <v>150.3574367674993</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.297491477797203</v>
+        <v>0.3203725212333124</v>
       </c>
       <c r="T90">
-        <v>4.905935375368753</v>
+        <v>5.351929500402276</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.069387587916662</v>
+        <v>2.046136041985014</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1027029773356644</v>
+        <v>0.1030029773356644</v>
       </c>
       <c r="C91">
-        <v>-104.9723909663123</v>
+        <v>-129.2482605386044</v>
       </c>
       <c r="D91">
-        <v>1678.562216322615</v>
+        <v>1674.896847955817</v>
       </c>
       <c r="E91">
-        <v>1365.384486739571</v>
+        <v>1385.994987945064</v>
       </c>
       <c r="F91">
-        <v>1834.334607288927</v>
+        <v>1854.945108494421</v>
       </c>
       <c r="G91">
         <v>50.8</v>
@@ -8877,28 +8877,28 @@
         <v>284.5</v>
       </c>
       <c r="M91">
-        <v>139.0425632325007</v>
+        <v>140.6048392238771</v>
       </c>
       <c r="N91">
-        <v>145.4574367674993</v>
+        <v>143.8951607761229</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>145.4574367674993</v>
+        <v>143.8951607761229</v>
       </c>
       <c r="Q91">
-        <v>150.3574367674993</v>
+        <v>148.7951607761229</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3203725212333124</v>
+        <v>0.3478297733566437</v>
       </c>
       <c r="T91">
-        <v>5.351929500402276</v>
+        <v>5.887122450442504</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.046136041985014</v>
+        <v>2.023401197074069</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1030029773356644</v>
+        <v>0.1033029773356644</v>
       </c>
       <c r="C92">
-        <v>-129.2482605386044</v>
+        <v>-153.5081573312482</v>
       </c>
       <c r="D92">
-        <v>1674.896847955817</v>
+        <v>1671.247452368666</v>
       </c>
       <c r="E92">
-        <v>1385.994987945064</v>
+        <v>1406.605489150558</v>
       </c>
       <c r="F92">
-        <v>1854.945108494421</v>
+        <v>1875.555609699914</v>
       </c>
       <c r="G92">
         <v>50.8</v>
@@ -8959,28 +8959,28 @@
         <v>284.5</v>
       </c>
       <c r="M92">
-        <v>140.6048392238771</v>
+        <v>142.1671152152535</v>
       </c>
       <c r="N92">
-        <v>143.8951607761229</v>
+        <v>142.3328847847465</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>143.8951607761229</v>
+        <v>142.3328847847465</v>
       </c>
       <c r="Q92">
-        <v>148.7951607761229</v>
+        <v>147.2328847847465</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3478297733566437</v>
+        <v>0.3813886370629374</v>
       </c>
       <c r="T92">
-        <v>5.887122450442504</v>
+        <v>6.541247167158339</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.023401197074069</v>
+        <v>2.001166019084244</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1033029773356644</v>
+        <v>0.1166669773356644</v>
       </c>
       <c r="C93">
-        <v>-153.5081573312482</v>
+        <v>-321.9810673502056</v>
       </c>
       <c r="D93">
-        <v>1671.247452368666</v>
+        <v>1523.385043555202</v>
       </c>
       <c r="E93">
-        <v>1406.605489150558</v>
+        <v>1427.215990356051</v>
       </c>
       <c r="F93">
-        <v>1875.555609699914</v>
+        <v>1896.166110905408</v>
       </c>
       <c r="G93">
         <v>50.8</v>
@@ -9041,45 +9041,45 @@
         <v>284.5</v>
       </c>
       <c r="M93">
-        <v>142.1671152152535</v>
+        <v>170.6549499814867</v>
       </c>
       <c r="N93">
-        <v>142.3328847847465</v>
+        <v>113.8450500185133</v>
       </c>
       <c r="O93">
         <v>0</v>
       </c>
       <c r="P93">
-        <v>142.3328847847465</v>
+        <v>113.8450500185133</v>
       </c>
       <c r="Q93">
-        <v>147.2328847847465</v>
+        <v>118.7450500185133</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3813886370629374</v>
+        <v>0.4233372166958047</v>
       </c>
       <c r="T93">
-        <v>6.541247167158339</v>
+        <v>7.358903063053133</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.001166019084244</v>
+        <v>1.667106638458853</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1166669773356644</v>
+        <v>0.1171089773356644</v>
       </c>
       <c r="C94">
-        <v>-321.9810673502056</v>
+        <v>-347.0362796303773</v>
       </c>
       <c r="D94">
-        <v>1523.385043555202</v>
+        <v>1518.940332480524</v>
       </c>
       <c r="E94">
-        <v>1427.215990356051</v>
+        <v>1447.826491561545</v>
       </c>
       <c r="F94">
-        <v>1896.166110905408</v>
+        <v>1916.776612110902</v>
       </c>
       <c r="G94">
         <v>50.8</v>
@@ -9123,28 +9123,28 @@
         <v>284.5</v>
       </c>
       <c r="M94">
-        <v>170.6549499814867</v>
+        <v>172.5098950899811</v>
       </c>
       <c r="N94">
-        <v>113.8450500185133</v>
+        <v>111.9901049100189</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>113.8450500185133</v>
+        <v>111.9901049100189</v>
       </c>
       <c r="Q94">
-        <v>118.7450500185133</v>
+        <v>116.8901049100189</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4233372166958047</v>
+        <v>0.4772711047952054</v>
       </c>
       <c r="T94">
-        <v>7.358903063053133</v>
+        <v>8.410174929203581</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.667106638458853</v>
+        <v>1.649180760625962</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1171089773356644</v>
+        <v>0.1175509773356644</v>
       </c>
       <c r="C95">
-        <v>-347.0362796303773</v>
+        <v>-372.0656311018074</v>
       </c>
       <c r="D95">
-        <v>1518.940332480524</v>
+        <v>1514.521482214588</v>
       </c>
       <c r="E95">
-        <v>1447.826491561545</v>
+        <v>1468.436992767039</v>
       </c>
       <c r="F95">
-        <v>1916.776612110902</v>
+        <v>1937.387113316395</v>
       </c>
       <c r="G95">
         <v>50.8</v>
@@ -9205,28 +9205,28 @@
         <v>284.5</v>
       </c>
       <c r="M95">
-        <v>172.5098950899811</v>
+        <v>174.3648401984756</v>
       </c>
       <c r="N95">
-        <v>111.9901049100189</v>
+        <v>110.1351598015244</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>111.9901049100189</v>
+        <v>110.1351598015244</v>
       </c>
       <c r="Q95">
-        <v>116.8901049100189</v>
+        <v>115.0351598015244</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4772711047952054</v>
+        <v>0.5491829555944064</v>
       </c>
       <c r="T95">
-        <v>8.410174929203581</v>
+        <v>9.811870750737516</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.649180760625962</v>
+        <v>1.63163628444909</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1175509773356644</v>
+        <v>0.1179929773356644</v>
       </c>
       <c r="C96">
-        <v>-372.0656311018074</v>
+        <v>-397.0693468099923</v>
       </c>
       <c r="D96">
-        <v>1514.521482214588</v>
+        <v>1510.128267711897</v>
       </c>
       <c r="E96">
-        <v>1468.436992767039</v>
+        <v>1489.047493972532</v>
       </c>
       <c r="F96">
-        <v>1937.387113316395</v>
+        <v>1957.997614521889</v>
       </c>
       <c r="G96">
         <v>50.8</v>
@@ -9287,28 +9287,28 @@
         <v>284.5</v>
       </c>
       <c r="M96">
-        <v>174.3648401984756</v>
+        <v>176.21978530697</v>
       </c>
       <c r="N96">
-        <v>110.1351598015244</v>
+        <v>108.28021469303</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>110.1351598015244</v>
+        <v>108.28021469303</v>
       </c>
       <c r="Q96">
-        <v>115.0351598015244</v>
+        <v>113.18021469303</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5491829555944064</v>
+        <v>0.6498595467132879</v>
       </c>
       <c r="T96">
-        <v>9.811870750737516</v>
+        <v>11.77424490088502</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.63163628444909</v>
+        <v>1.614461165665416</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1179929773356644</v>
+        <v>0.1184349773356644</v>
       </c>
       <c r="C97">
-        <v>-397.0693468099923</v>
+        <v>-422.0476491967997</v>
       </c>
       <c r="D97">
-        <v>1510.128267711897</v>
+        <v>1505.760466530583</v>
       </c>
       <c r="E97">
-        <v>1489.047493972532</v>
+        <v>1509.657995178026</v>
       </c>
       <c r="F97">
-        <v>1957.997614521889</v>
+        <v>1978.608115727382</v>
       </c>
       <c r="G97">
         <v>50.8</v>
@@ -9369,28 +9369,28 @@
         <v>284.5</v>
       </c>
       <c r="M97">
-        <v>176.21978530697</v>
+        <v>178.0747304154644</v>
       </c>
       <c r="N97">
-        <v>108.28021469303</v>
+        <v>106.4252695845356</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>108.28021469303</v>
+        <v>106.4252695845356</v>
       </c>
       <c r="Q97">
-        <v>113.18021469303</v>
+        <v>111.3252695845356</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6498595467132879</v>
+        <v>0.8008744333916104</v>
       </c>
       <c r="T97">
-        <v>11.77424490088502</v>
+        <v>14.71780612610629</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.614461165665416</v>
+        <v>1.597643861856401</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1184349773356644</v>
+        <v>0.1188769773356644</v>
       </c>
       <c r="C98">
-        <v>-422.0476491967995</v>
+        <v>-447.0007581380091</v>
       </c>
       <c r="D98">
-        <v>1505.760466530583</v>
+        <v>1501.417858794867</v>
       </c>
       <c r="E98">
-        <v>1509.657995178026</v>
+        <v>1530.268496383519</v>
       </c>
       <c r="F98">
-        <v>1978.608115727382</v>
+        <v>1999.218616932876</v>
       </c>
       <c r="G98">
         <v>50.8</v>
@@ -9451,28 +9451,28 @@
         <v>284.5</v>
       </c>
       <c r="M98">
-        <v>178.0747304154644</v>
+        <v>179.9296755239588</v>
       </c>
       <c r="N98">
-        <v>106.4252695845356</v>
+        <v>104.5703244760412</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>106.4252695845356</v>
+        <v>104.5703244760412</v>
       </c>
       <c r="Q98">
-        <v>111.3252695845356</v>
+        <v>109.4703244760412</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8008744333916084</v>
+        <v>1.052565911188811</v>
       </c>
       <c r="T98">
-        <v>14.71780612610625</v>
+        <v>19.623741501475</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.597643861856401</v>
+        <v>1.581173306579531</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1188769773356644</v>
+        <v>0.1193189773356644</v>
       </c>
       <c r="C99">
-        <v>-447.0007581380091</v>
+        <v>-471.9288909802133</v>
       </c>
       <c r="D99">
-        <v>1501.417858794867</v>
+        <v>1497.100227158156</v>
       </c>
       <c r="E99">
-        <v>1530.268496383519</v>
+        <v>1550.878997589013</v>
       </c>
       <c r="F99">
-        <v>1999.218616932876</v>
+        <v>2019.829118138369</v>
       </c>
       <c r="G99">
         <v>50.8</v>
@@ -9533,28 +9533,28 @@
         <v>284.5</v>
       </c>
       <c r="M99">
-        <v>179.9296755239588</v>
+        <v>181.7846206324532</v>
       </c>
       <c r="N99">
-        <v>104.5703244760412</v>
+        <v>102.7153793675468</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>104.5703244760412</v>
+        <v>102.7153793675468</v>
       </c>
       <c r="Q99">
-        <v>109.4703244760412</v>
+        <v>107.6153793675468</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.052565911188811</v>
+        <v>1.555948866783217</v>
       </c>
       <c r="T99">
-        <v>19.623741501475</v>
+        <v>29.43561225221249</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.581173306579531</v>
+        <v>1.565038885083821</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1193189773356644</v>
+        <v>0.1197609773356644</v>
       </c>
       <c r="C100">
-        <v>-471.9288909802133</v>
+        <v>-496.8322625770736</v>
       </c>
       <c r="D100">
-        <v>1497.100227158156</v>
+        <v>1492.807356766789</v>
       </c>
       <c r="E100">
-        <v>1550.878997589013</v>
+        <v>1571.489498794506</v>
       </c>
       <c r="F100">
-        <v>2019.829118138369</v>
+        <v>2040.439619343863</v>
       </c>
       <c r="G100">
         <v>50.8</v>
@@ -9615,28 +9615,28 @@
         <v>284.5</v>
       </c>
       <c r="M100">
-        <v>181.7846206324532</v>
+        <v>183.6395657409477</v>
       </c>
       <c r="N100">
-        <v>102.7153793675468</v>
+        <v>100.8604342590523</v>
       </c>
       <c r="O100">
         <v>0</v>
       </c>
       <c r="P100">
-        <v>102.7153793675468</v>
+        <v>100.8604342590523</v>
       </c>
       <c r="Q100">
-        <v>107.6153793675468</v>
+        <v>105.7604342590523</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.555948866783217</v>
+        <v>3.066097733566433</v>
       </c>
       <c r="T100">
-        <v>29.43561225221249</v>
+        <v>58.87122450442499</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.565038885083821</v>
+        <v>1.549230411497116</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1197609773356644</v>
-      </c>
-      <c r="C101">
-        <v>-496.8322625770736</v>
-      </c>
-      <c r="D101">
-        <v>1492.807356766789</v>
-      </c>
-      <c r="E101">
-        <v>1571.489498794506</v>
-      </c>
-      <c r="F101">
-        <v>2040.439619343863</v>
-      </c>
-      <c r="G101">
-        <v>50.8</v>
-      </c>
-      <c r="H101">
-        <v>1592.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>289.4</v>
-      </c>
-      <c r="K101">
-        <v>4.9</v>
-      </c>
-      <c r="L101">
-        <v>284.5</v>
-      </c>
-      <c r="M101">
-        <v>183.6395657409477</v>
-      </c>
-      <c r="N101">
-        <v>100.8604342590523</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>100.8604342590523</v>
-      </c>
-      <c r="Q101">
-        <v>105.7604342590523</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.066097733566433</v>
-      </c>
-      <c r="T101">
-        <v>58.87122450442499</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.09</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.549230411497116</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
